--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-11_User_Access_Maintenance/BIBS_RTM_BRD-11_Test_Cases_and_Traceability_v1.1.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-11_User_Access_Maintenance/BIBS_RTM_BRD-11_Test_Cases_and_Traceability_v1.1.xlsx
@@ -29,7 +29,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'FR items'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Test cases'!$A$4:$S$307</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'Test cases'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Change requests'!$A$4:$G$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Change requests'!$A$4:$G$20</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'Change requests'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Answered in the BDOI FRS'!$A$4:$E$48</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Answered in the BDOI FRS'!$4:$4</definedName>
@@ -939,7 +939,7 @@
         </is>
       </c>
       <c r="D25" s="14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="26">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="C18" s="14" t="inlineStr">
         <is>
-          <t>CR-UA-nnn: change request (orange); OB-UA-nn: offered as standard (green)</t>
+          <t>CR-UA-nnn: change request (orange); OB-UA-nn: offered by iNXT BrokerVerse OOTB (green); IS-UA-nn: integration scope</t>
         </is>
       </c>
       <c r="D18" s="14" t="inlineStr"/>
@@ -8863,7 +8863,7 @@
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>CR-UA-007 (change request)</t>
+          <t>CR-UA-007 (change request); IS-UA-03 (integration scope)</t>
         </is>
       </c>
       <c r="E6" s="12" t="n">
@@ -8995,7 +8995,7 @@
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>OB-UA-04 (offered as standard)</t>
+          <t>IS-UA-01 (integration scope)</t>
         </is>
       </c>
       <c r="E10" s="12" t="n">
@@ -9094,7 +9094,7 @@
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>OB-UA-05 (offered as standard)</t>
+          <t>IS-UA-02 (integration scope)</t>
         </is>
       </c>
       <c r="E13" s="12" t="n">
@@ -9160,7 +9160,7 @@
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>OB-UA-04 (offered as standard)</t>
+          <t>IS-UA-01 (integration scope)</t>
         </is>
       </c>
       <c r="E15" s="12" t="n">
@@ -9292,7 +9292,7 @@
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>CR-UA-007 (change request); OB-UA-10 (offered as standard)</t>
+          <t>CR-UA-007 (change request); CR-UA-016 (change request)</t>
         </is>
       </c>
       <c r="E19" s="12" t="n">
@@ -9457,7 +9457,7 @@
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>OB-UA-06 (offered as standard)</t>
+          <t>CR-UA-008 (change request)</t>
         </is>
       </c>
       <c r="E24" s="12" t="n">
@@ -9523,7 +9523,7 @@
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>OB-UA-07 (offered as standard)</t>
+          <t>CR-UA-009 (change request)</t>
         </is>
       </c>
       <c r="E26" s="12" t="n">
@@ -9688,7 +9688,7 @@
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>OB-UA-03 (offered as standard)</t>
+          <t>CR-UA-003 (change request)</t>
         </is>
       </c>
       <c r="E31" s="12" t="n">
@@ -9754,7 +9754,7 @@
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>OB-UA-02 (offered as standard)</t>
+          <t>OB-UA-02 (offered by iNXT BrokerVerse OOTB)</t>
         </is>
       </c>
       <c r="E33" s="12" t="n">
@@ -10579,7 +10579,7 @@
       </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
-          <t>OB-UA-01 (offered as standard)</t>
+          <t>OB-UA-01 (offered by iNXT BrokerVerse OOTB)</t>
         </is>
       </c>
       <c r="E58" s="12" t="n">
@@ -10612,7 +10612,7 @@
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>OB-UA-09 (offered as standard)</t>
+          <t>In the BRD</t>
         </is>
       </c>
       <c r="E59" s="12" t="n">
@@ -10645,7 +10645,7 @@
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
-          <t>OB-UA-08 (offered as standard)</t>
+          <t>CR-UA-013 (change request)</t>
         </is>
       </c>
       <c r="E60" s="12" t="n">
@@ -35606,7 +35606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -35686,7 +35686,7 @@
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>Offered as standard (OB-UA-01, green in the FRS)</t>
+          <t>Offered by iNXT BrokerVerse OOTB (OB-UA-01, green in the FRS)</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
@@ -35723,7 +35723,7 @@
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>Offered as standard (OB-UA-02, green in the FRS)</t>
+          <t>Offered by iNXT BrokerVerse OOTB (OB-UA-02, green in the FRS)</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
@@ -35760,7 +35760,7 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Offered as standard (OB-UA-03, green in the FRS)</t>
+          <t>Change request (orange in the FRS)</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -35770,17 +35770,17 @@
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>FRUM.001.06</t>
+          <t>FRUM.001.06; Annex N.4, Annex Q.5</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>BRD 4.001.1</t>
+          <t>Not in BRD</t>
         </is>
       </c>
       <c r="F7" s="12" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Candidate - for decision</t>
         </is>
       </c>
       <c r="G7" s="12" t="inlineStr">
@@ -35834,7 +35834,7 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>Offered as standard (OB-UA-04, green in the FRS)</t>
+          <t>Integration scope (IS-UA-01, grey label in the FRS)</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
@@ -35871,7 +35871,7 @@
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>Offered as standard (OB-UA-05, green in the FRS)</t>
+          <t>Integration scope (IS-UA-02, grey label in the FRS)</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
@@ -35945,12 +35945,12 @@
       </c>
       <c r="B12" s="12" t="inlineStr">
         <is>
-          <t>Offered as standard (OB-UA-06, green in the FRS)</t>
+          <t>Change request (orange in the FRS)</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>Conflicting permission combinations inside a role</t>
+          <t>No conflicting permissions inside a group profile</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
@@ -35960,12 +35960,12 @@
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
-          <t>BRD 4.002.2</t>
+          <t>Not in BRD</t>
         </is>
       </c>
       <c r="F12" s="12" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Candidate - for decision</t>
         </is>
       </c>
       <c r="G12" s="12" t="inlineStr">
@@ -35982,7 +35982,7 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Offered as standard (OB-UA-07, green in the FRS)</t>
+          <t>Change request (orange in the FRS)</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
@@ -35992,17 +35992,17 @@
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>FRUM.007.02</t>
+          <t>FRUM.007.02; Annex V</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>BRD p.18</t>
+          <t>Not in BRD</t>
         </is>
       </c>
       <c r="F13" s="12" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Candidate - for decision</t>
         </is>
       </c>
       <c r="G13" s="12" t="inlineStr">
@@ -36093,27 +36093,27 @@
       </c>
       <c r="B16" s="12" t="inlineStr">
         <is>
-          <t>Change request (orange in the FRS)</t>
+          <t>Offered by iNXT BrokerVerse OOTB (OB-UA-05, green in the FRS)</t>
         </is>
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>Monthly access review report to Information Security</t>
+          <t>Monthly access review report</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>Annex V, Annex Q.5 (UA-Q51)</t>
+          <t>FRUM.007</t>
         </is>
       </c>
       <c r="E16" s="12" t="inlineStr">
         <is>
-          <t>Not in BRD (BRD p.11 lists report volumes only)</t>
+          <t>BRD NFR p.11</t>
         </is>
       </c>
       <c r="F16" s="12" t="inlineStr">
         <is>
-          <t>Candidate - for decision</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="G16" s="12" t="inlineStr">
@@ -36130,7 +36130,7 @@
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Offered as standard (OB-UA-08, green in the FRS)</t>
+          <t>Change request (orange in the FRS)</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
@@ -36140,17 +36140,17 @@
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>FRUM.013.01</t>
+          <t>FRUM.013.01; Annex T</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>BRD 1.006.1.1, 1.008.1.4, 2.002.1</t>
+          <t>Not in BRD</t>
         </is>
       </c>
       <c r="F17" s="12" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Candidate - for decision</t>
         </is>
       </c>
       <c r="G17" s="12" t="inlineStr">
@@ -36233,12 +36233,49 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>CR-UA-016</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>Change request (orange in the FRS)</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>Emergency role edit</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>FRUM.005.01; Annex J</t>
+        </is>
+      </c>
+      <c r="E20" s="12" t="inlineStr">
+        <is>
+          <t>Not in BRD</t>
+        </is>
+      </c>
+      <c r="F20" s="12" t="inlineStr">
+        <is>
+          <t>Candidate - for decision</t>
+        </is>
+      </c>
+      <c r="G20" s="12" t="inlineStr">
+        <is>
+          <t>TC-FRUM-005.01-AC01, TC-FRUM-005.01-AC02, TC-FRUM-005.01-AC03, TC-UA-040.1-01, TC-UA-040.2-01</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:G19"/>
+  <autoFilter ref="A4:G20"/>
   <mergeCells count="1">
     <mergeCell ref="A2:G2"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G519">
+  <conditionalFormatting sqref="A5:G520">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
     </cfRule>

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-11_User_Access_Maintenance/BIBS_RTM_BRD-11_Test_Cases_and_Traceability_v1.1.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-11_User_Access_Maintenance/BIBS_RTM_BRD-11_Test_Cases_and_Traceability_v1.1.xlsx
@@ -9457,7 +9457,7 @@
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>CR-UA-008 (change request)</t>
+          <t>In the BRD</t>
         </is>
       </c>
       <c r="E24" s="12" t="n">
@@ -9523,7 +9523,7 @@
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>CR-UA-009 (change request)</t>
+          <t>In the BRD</t>
         </is>
       </c>
       <c r="E26" s="12" t="n">
@@ -10645,7 +10645,7 @@
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
-          <t>CR-UA-013 (change request)</t>
+          <t>In the BRD</t>
         </is>
       </c>
       <c r="E60" s="12" t="n">
@@ -35945,12 +35945,12 @@
       </c>
       <c r="B12" s="12" t="inlineStr">
         <is>
-          <t>Change request (orange in the FRS)</t>
+          <t>BRD requirement (black in the FRS)</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>No conflicting permissions inside a group profile</t>
+          <t>Conflicting permission combinations inside a role</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
@@ -35960,12 +35960,12 @@
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
-          <t>Not in BRD</t>
+          <t>UAM BRD NFR System Operation 2.b "Master data management tool enforces referential integrity rules and data validation rules - b.1) Prevents entry of incorrect data" applied to "user and role data"</t>
         </is>
       </c>
       <c r="F12" s="12" t="inlineStr">
         <is>
-          <t>Candidate - for decision</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="G12" s="12" t="inlineStr">
@@ -35982,7 +35982,7 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Change request (orange in the FRS)</t>
+          <t>BRD requirement (black in the FRS)</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
@@ -35992,17 +35992,17 @@
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>FRUM.007.02; Annex V</t>
+          <t>FRUM.007.02</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Not in BRD</t>
+          <t>UAM BRD NFR 1.g "Has query or report to display roles assigned to users. Report can be exported.", Other BU NFR 6 "Availability of Audit log reports" and the report samples A to D; the file-name convention of the exports is part of the exported reports</t>
         </is>
       </c>
       <c r="F13" s="12" t="inlineStr">
         <is>
-          <t>Candidate - for decision</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="G13" s="12" t="inlineStr">
@@ -36061,7 +36061,7 @@
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>Approval times, reminders and escalation</t>
+          <t>Approval times and reminders of access requests</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
@@ -36071,7 +36071,7 @@
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Not in BRD</t>
+          <t>Not in BRD (UAM BRD Other BU NFR 11 asks for a configurable, monitored workflow with escalation of risky changes, not for time limits or reminders)</t>
         </is>
       </c>
       <c r="F15" s="12" t="inlineStr">
@@ -36130,7 +36130,7 @@
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Change request (orange in the FRS)</t>
+          <t>BRD requirement (black in the FRS)</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
@@ -36140,17 +36140,17 @@
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>FRUM.013.01; Annex T</t>
+          <t>FRUM.013.01</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Not in BRD</t>
+          <t>UAM BRD Other BU NFR 10 "With Notification for access changes" and BRD 1.006.1.1, 1.008.1.4, 2.002.1</t>
         </is>
       </c>
       <c r="F17" s="12" t="inlineStr">
         <is>
-          <t>Candidate - for decision</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="G17" s="12" t="inlineStr">
@@ -36172,7 +36172,7 @@
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>Temporary access with an end date</t>
+          <t>End date captured on the granting request (temporary access)</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr">
@@ -36182,7 +36182,7 @@
       </c>
       <c r="E18" s="12" t="inlineStr">
         <is>
-          <t>Not in BRD (BRD NFR 1.k asks for an effective date only)</t>
+          <t>Not in BRD (BRD NFR 1.k asks for an effective date of user and role changes; the removal of access on a date is that BRD item)</t>
         </is>
       </c>
       <c r="F18" s="12" t="inlineStr">

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-11_User_Access_Maintenance/BIBS_RTM_BRD-11_Test_Cases_and_Traceability_v1.1.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-11_User_Access_Maintenance/BIBS_RTM_BRD-11_Test_Cases_and_Traceability_v1.1.xlsx
@@ -1405,7 +1405,7 @@
       </c>
       <c r="C18" s="14" t="inlineStr">
         <is>
-          <t>CR-UA-nnn: change request (orange); OB-UA-nn: offered by iNXT BrokerVerse OOTB (green); IS-UA-nn: integration scope</t>
+          <t>CR-UA-nnn: change request (orange); OB-UA-nn: offered by iNXT BrokerVerse OOTB (green, or a BRD requirement when so marked); IS-UA-nn: integration scope</t>
         </is>
       </c>
       <c r="D18" s="14" t="inlineStr"/>
@@ -10579,7 +10579,7 @@
       </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
-          <t>OB-UA-01 (offered by iNXT BrokerVerse OOTB)</t>
+          <t>OB-UA-01 (BRD requirement, offered by iNXT BrokerVerse OOTB, no effort)</t>
         </is>
       </c>
       <c r="E58" s="12" t="n">
@@ -35686,7 +35686,7 @@
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>Offered by iNXT BrokerVerse OOTB (OB-UA-01, green in the FRS)</t>
+          <t>BRD requirement, offered by iNXT BrokerVerse OOTB (OB-UA-01, black in the FRS, no effort)</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
@@ -35701,7 +35701,7 @@
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>BRD NFR p.17 (11)</t>
+          <t>UAM BRD Other BU NFR 2-3 "Role-Based Access Control - Define roles and assign permission; Permission Management", NFR System Operation 2.b data validation rules on user and role data, and the Operations addendum "Clear segregation of duties across Marketing, Cashiering, and Disbursement"</t>
         </is>
       </c>
       <c r="F5" s="12" t="inlineStr">

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-11_User_Access_Maintenance/BIBS_RTM_BRD-11_Test_Cases_and_Traceability_v1.1.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-11_User_Access_Maintenance/BIBS_RTM_BRD-11_Test_Cases_and_Traceability_v1.1.xlsx
@@ -10249,7 +10249,7 @@
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>In the BRD</t>
+          <t>IS-UA-06 (integration scope)</t>
         </is>
       </c>
       <c r="E48" s="12" t="n">
@@ -10282,7 +10282,7 @@
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>In the BRD</t>
+          <t>IS-UA-06 (integration scope)</t>
         </is>
       </c>
       <c r="E49" s="12" t="n">
@@ -10315,7 +10315,7 @@
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
-          <t>In the BRD</t>
+          <t>IS-UA-06 (integration scope)</t>
         </is>
       </c>
       <c r="E50" s="12" t="n">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>In the BRD</t>
+          <t>IS-UA-08 (integration scope)</t>
         </is>
       </c>
       <c r="E52" s="12" t="n">
@@ -10414,7 +10414,7 @@
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>In the BRD</t>
+          <t>IS-UA-08 (integration scope)</t>
         </is>
       </c>
       <c r="E53" s="12" t="n">
@@ -10447,7 +10447,7 @@
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>In the BRD</t>
+          <t>IS-UA-08 (integration scope)</t>
         </is>
       </c>
       <c r="E54" s="12" t="n">
@@ -10480,7 +10480,7 @@
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>In the BRD</t>
+          <t>IS-UA-08 (integration scope)</t>
         </is>
       </c>
       <c r="E55" s="12" t="n">
@@ -10513,7 +10513,7 @@
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>In the BRD</t>
+          <t>IS-UA-08 (integration scope)</t>
         </is>
       </c>
       <c r="E56" s="12" t="n">
@@ -10546,7 +10546,7 @@
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>In the BRD</t>
+          <t>IS-UA-07 (integration scope)</t>
         </is>
       </c>
       <c r="E57" s="12" t="n">
@@ -10645,7 +10645,7 @@
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
-          <t>In the BRD</t>
+          <t>IS-UA-09 (integration scope)</t>
         </is>
       </c>
       <c r="E60" s="12" t="n">

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-11_User_Access_Maintenance/BIBS_RTM_BRD-11_Test_Cases_and_Traceability_v1.1.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-11_User_Access_Maintenance/BIBS_RTM_BRD-11_Test_Cases_and_Traceability_v1.1.xlsx
@@ -713,7 +713,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B4:E35"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -723,13 +723,16 @@
     <col width="16" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="40" customHeight="1"/>
+    <row r="3"/>
     <row r="4" ht="6" customHeight="1">
       <c r="B4" s="1" t="n"/>
       <c r="C4" s="1" t="n"/>
       <c r="D4" s="1" t="n"/>
       <c r="E4" s="1" t="n"/>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="2" t="inlineStr">
         <is>
@@ -758,6 +761,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="B11" s="6" t="inlineStr">
         <is>
@@ -830,6 +834,7 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="B18" s="9" t="inlineStr">
         <is>
@@ -972,6 +977,7 @@
         <v>10</v>
       </c>
     </row>
+    <row r="28"/>
     <row r="29">
       <c r="B29" s="9" t="inlineStr">
         <is>
@@ -1003,6 +1009,8 @@
       </c>
       <c r="C32" s="16" t="inlineStr"/>
     </row>
+    <row r="33"/>
+    <row r="34"/>
     <row r="35" ht="26" customHeight="1">
       <c r="B35" s="18" t="inlineStr">
         <is>
@@ -1164,6 +1172,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
@@ -5276,7 +5285,7 @@
       </c>
       <c r="G91" s="12" t="inlineStr">
         <is>
-          <t>WT-B.4, WT-D.5</t>
+          <t>WT-B.4</t>
         </is>
       </c>
     </row>
@@ -5311,7 +5320,7 @@
       </c>
       <c r="G92" s="12" t="inlineStr">
         <is>
-          <t>WT-B.4, WT-D.5</t>
+          <t>WT-B.4</t>
         </is>
       </c>
     </row>
@@ -5346,7 +5355,7 @@
       </c>
       <c r="G93" s="12" t="inlineStr">
         <is>
-          <t>WT-B.4, WT-D.5</t>
+          <t>WT-B.4</t>
         </is>
       </c>
     </row>
@@ -5381,7 +5390,7 @@
       </c>
       <c r="G94" s="12" t="inlineStr">
         <is>
-          <t>WT-B.4, WT-D.5</t>
+          <t>WT-B.4</t>
         </is>
       </c>
     </row>
@@ -5416,7 +5425,7 @@
       </c>
       <c r="G95" s="12" t="inlineStr">
         <is>
-          <t>WT-B.4, WT-D.5</t>
+          <t>WT-B.4</t>
         </is>
       </c>
     </row>
@@ -5451,7 +5460,7 @@
       </c>
       <c r="G96" s="12" t="inlineStr">
         <is>
-          <t>WT-B.4, WT-D.5</t>
+          <t>WT-B.4</t>
         </is>
       </c>
     </row>
@@ -5486,7 +5495,7 @@
       </c>
       <c r="G97" s="12" t="inlineStr">
         <is>
-          <t>WT-B.4, WT-D.5</t>
+          <t>WT-B.4</t>
         </is>
       </c>
     </row>
@@ -5521,7 +5530,7 @@
       </c>
       <c r="G98" s="12" t="inlineStr">
         <is>
-          <t>WT-B.4, WT-D.5</t>
+          <t>WT-B.4</t>
         </is>
       </c>
     </row>
@@ -5556,7 +5565,7 @@
       </c>
       <c r="G99" s="12" t="inlineStr">
         <is>
-          <t>WT-B.4, WT-D.5</t>
+          <t>WT-B.4</t>
         </is>
       </c>
     </row>
@@ -5591,7 +5600,7 @@
       </c>
       <c r="G100" s="12" t="inlineStr">
         <is>
-          <t>WT-B.4, WT-D.5</t>
+          <t>WT-B.4</t>
         </is>
       </c>
     </row>
@@ -5626,7 +5635,7 @@
       </c>
       <c r="G101" s="12" t="inlineStr">
         <is>
-          <t>WT-B.4, WT-D.5</t>
+          <t>WT-B.4</t>
         </is>
       </c>
     </row>
@@ -5661,7 +5670,7 @@
       </c>
       <c r="G102" s="12" t="inlineStr">
         <is>
-          <t>WT-B.4, WT-D.5</t>
+          <t>WT-B.4</t>
         </is>
       </c>
     </row>
@@ -5696,7 +5705,7 @@
       </c>
       <c r="G103" s="12" t="inlineStr">
         <is>
-          <t>WT-B.4, WT-D.5</t>
+          <t>WT-B.4</t>
         </is>
       </c>
     </row>
@@ -5731,7 +5740,7 @@
       </c>
       <c r="G104" s="12" t="inlineStr">
         <is>
-          <t>WT-B.4, WT-D.5</t>
+          <t>WT-B.4</t>
         </is>
       </c>
     </row>
@@ -5766,7 +5775,7 @@
       </c>
       <c r="G105" s="12" t="inlineStr">
         <is>
-          <t>WT-B.4, WT-D.5</t>
+          <t>WT-B.4</t>
         </is>
       </c>
     </row>
@@ -5801,7 +5810,7 @@
       </c>
       <c r="G106" s="12" t="inlineStr">
         <is>
-          <t>WT-B.4, WT-D.5</t>
+          <t>WT-B.4</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5845,7 @@
       </c>
       <c r="G107" s="12" t="inlineStr">
         <is>
-          <t>WT-B.4, WT-D.5</t>
+          <t>WT-B.4</t>
         </is>
       </c>
     </row>
@@ -5871,7 +5880,7 @@
       </c>
       <c r="G108" s="12" t="inlineStr">
         <is>
-          <t>WT-B.4, WT-D.5</t>
+          <t>WT-B.4</t>
         </is>
       </c>
     </row>
@@ -5906,7 +5915,7 @@
       </c>
       <c r="G109" s="12" t="inlineStr">
         <is>
-          <t>WT-B.4, WT-D.5</t>
+          <t>WT-B.4</t>
         </is>
       </c>
     </row>
@@ -5941,7 +5950,7 @@
       </c>
       <c r="G110" s="12" t="inlineStr">
         <is>
-          <t>WT-B.4, WT-D.5</t>
+          <t>WT-B.4</t>
         </is>
       </c>
     </row>
@@ -5976,7 +5985,7 @@
       </c>
       <c r="G111" s="12" t="inlineStr">
         <is>
-          <t>WT-B.4, WT-D.5</t>
+          <t>WT-B.4</t>
         </is>
       </c>
     </row>
@@ -6011,7 +6020,7 @@
       </c>
       <c r="G112" s="12" t="inlineStr">
         <is>
-          <t>WT-B.4, WT-D.5</t>
+          <t>WT-B.4</t>
         </is>
       </c>
     </row>
@@ -6046,7 +6055,7 @@
       </c>
       <c r="G113" s="12" t="inlineStr">
         <is>
-          <t>WT-B.4, WT-D.5</t>
+          <t>WT-B.4</t>
         </is>
       </c>
     </row>
@@ -6081,7 +6090,7 @@
       </c>
       <c r="G114" s="12" t="inlineStr">
         <is>
-          <t>WT-B.4, WT-D.5</t>
+          <t>WT-B.4</t>
         </is>
       </c>
     </row>
@@ -6116,7 +6125,7 @@
       </c>
       <c r="G115" s="12" t="inlineStr">
         <is>
-          <t>WT-B.4, WT-D.5</t>
+          <t>WT-B.4</t>
         </is>
       </c>
     </row>
@@ -6151,7 +6160,7 @@
       </c>
       <c r="G116" s="12" t="inlineStr">
         <is>
-          <t>WT-B.4, WT-D.5</t>
+          <t>WT-B.4</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6195,7 @@
       </c>
       <c r="G117" s="12" t="inlineStr">
         <is>
-          <t>WT-B.4, WT-D.5</t>
+          <t>WT-B.4</t>
         </is>
       </c>
     </row>
@@ -6221,7 +6230,7 @@
       </c>
       <c r="G118" s="12" t="inlineStr">
         <is>
-          <t>WT-B.4, WT-D.5</t>
+          <t>WT-B.4</t>
         </is>
       </c>
     </row>
@@ -6256,7 +6265,7 @@
       </c>
       <c r="G119" s="12" t="inlineStr">
         <is>
-          <t>WT-B.4, WT-D.5</t>
+          <t>WT-B.4</t>
         </is>
       </c>
     </row>
@@ -6291,7 +6300,7 @@
       </c>
       <c r="G120" s="12" t="inlineStr">
         <is>
-          <t>WT-B.4, WT-D.5</t>
+          <t>WT-B.4</t>
         </is>
       </c>
     </row>
@@ -6326,7 +6335,7 @@
       </c>
       <c r="G121" s="12" t="inlineStr">
         <is>
-          <t>WT-B.4, WT-D.5</t>
+          <t>WT-B.4</t>
         </is>
       </c>
     </row>
@@ -6361,7 +6370,7 @@
       </c>
       <c r="G122" s="12" t="inlineStr">
         <is>
-          <t>WT-B.4, WT-D.5</t>
+          <t>WT-B.4</t>
         </is>
       </c>
     </row>
@@ -6396,7 +6405,7 @@
       </c>
       <c r="G123" s="12" t="inlineStr">
         <is>
-          <t>WT-B.4, WT-D.5</t>
+          <t>WT-B.4</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6440,7 @@
       </c>
       <c r="G124" s="12" t="inlineStr">
         <is>
-          <t>WT-B.4, WT-D.5</t>
+          <t>WT-B.4</t>
         </is>
       </c>
     </row>
@@ -6466,7 +6475,7 @@
       </c>
       <c r="G125" s="12" t="inlineStr">
         <is>
-          <t>WT-B.4, WT-D.5</t>
+          <t>WT-B.4</t>
         </is>
       </c>
     </row>
@@ -6501,7 +6510,7 @@
       </c>
       <c r="G126" s="12" t="inlineStr">
         <is>
-          <t>WT-A.8, WT-D.2, WT-D.3, WT-D.4</t>
+          <t>WT-A.8, WT-D.2, WT-D.3, WT-D.4, WT-D.5</t>
         </is>
       </c>
     </row>
@@ -6536,7 +6545,7 @@
       </c>
       <c r="G127" s="12" t="inlineStr">
         <is>
-          <t>WT-A.8, WT-D.2, WT-D.3, WT-D.4</t>
+          <t>WT-A.8, WT-D.2, WT-D.3, WT-D.4, WT-D.5</t>
         </is>
       </c>
     </row>
@@ -6571,7 +6580,7 @@
       </c>
       <c r="G128" s="12" t="inlineStr">
         <is>
-          <t>WT-A.8, WT-D.2, WT-D.3, WT-D.4</t>
+          <t>WT-A.8, WT-D.2, WT-D.3, WT-D.4, WT-D.5</t>
         </is>
       </c>
     </row>
@@ -6606,7 +6615,7 @@
       </c>
       <c r="G129" s="12" t="inlineStr">
         <is>
-          <t>WT-A.8, WT-D.2, WT-D.3, WT-D.4</t>
+          <t>WT-A.8, WT-D.2, WT-D.3, WT-D.4, WT-D.5</t>
         </is>
       </c>
     </row>
@@ -6641,7 +6650,7 @@
       </c>
       <c r="G130" s="12" t="inlineStr">
         <is>
-          <t>WT-A.8, WT-D.2, WT-D.3, WT-D.4</t>
+          <t>WT-A.8, WT-D.2, WT-D.3, WT-D.4, WT-D.5</t>
         </is>
       </c>
     </row>
@@ -6676,7 +6685,7 @@
       </c>
       <c r="G131" s="12" t="inlineStr">
         <is>
-          <t>WT-A.8, WT-D.2, WT-D.3, WT-D.4</t>
+          <t>WT-A.8, WT-D.2, WT-D.3, WT-D.4, WT-D.5</t>
         </is>
       </c>
     </row>
@@ -6711,7 +6720,7 @@
       </c>
       <c r="G132" s="12" t="inlineStr">
         <is>
-          <t>WT-A.8, WT-D.2, WT-D.3, WT-D.4</t>
+          <t>WT-A.8, WT-D.2, WT-D.3, WT-D.4, WT-D.5</t>
         </is>
       </c>
     </row>
@@ -6746,7 +6755,7 @@
       </c>
       <c r="G133" s="12" t="inlineStr">
         <is>
-          <t>WT-A.8, WT-D.2, WT-D.3, WT-D.4</t>
+          <t>WT-A.8, WT-D.2, WT-D.3, WT-D.4, WT-D.5</t>
         </is>
       </c>
     </row>
@@ -6781,7 +6790,7 @@
       </c>
       <c r="G134" s="12" t="inlineStr">
         <is>
-          <t>WT-A.8, WT-D.1, WT-D.2, WT-D.3, WT-D.4</t>
+          <t>WT-A.8, WT-D.1, WT-D.2, WT-D.3, WT-D.4, WT-D.5</t>
         </is>
       </c>
     </row>
@@ -6816,7 +6825,7 @@
       </c>
       <c r="G135" s="12" t="inlineStr">
         <is>
-          <t>WT-A.8, WT-D.1, WT-D.2, WT-D.3, WT-D.4</t>
+          <t>WT-A.8, WT-D.1, WT-D.2, WT-D.3, WT-D.4, WT-D.5</t>
         </is>
       </c>
     </row>
@@ -6851,7 +6860,7 @@
       </c>
       <c r="G136" s="12" t="inlineStr">
         <is>
-          <t>WT-A.8, WT-D.1, WT-D.2, WT-D.3, WT-D.4</t>
+          <t>WT-A.8, WT-D.1, WT-D.2, WT-D.3, WT-D.4, WT-D.5</t>
         </is>
       </c>
     </row>
@@ -6886,7 +6895,7 @@
       </c>
       <c r="G137" s="12" t="inlineStr">
         <is>
-          <t>WT-A.8, WT-D.1, WT-D.2, WT-D.3, WT-D.4</t>
+          <t>WT-A.8, WT-D.1, WT-D.2, WT-D.3, WT-D.4, WT-D.5</t>
         </is>
       </c>
     </row>
@@ -6921,7 +6930,7 @@
       </c>
       <c r="G138" s="12" t="inlineStr">
         <is>
-          <t>WT-A.8, WT-D.1, WT-D.2, WT-D.3, WT-D.4</t>
+          <t>WT-A.8, WT-D.1, WT-D.2, WT-D.3, WT-D.4, WT-D.5</t>
         </is>
       </c>
     </row>
@@ -6956,7 +6965,7 @@
       </c>
       <c r="G139" s="12" t="inlineStr">
         <is>
-          <t>WT-A.8, WT-D.1, WT-D.2, WT-D.3, WT-D.4</t>
+          <t>WT-A.8, WT-D.1, WT-D.2, WT-D.3, WT-D.4, WT-D.5</t>
         </is>
       </c>
     </row>
@@ -6991,7 +7000,7 @@
       </c>
       <c r="G140" s="12" t="inlineStr">
         <is>
-          <t>WT-A.8, WT-D.1, WT-D.2, WT-D.3, WT-D.4</t>
+          <t>WT-A.8, WT-D.1, WT-D.2, WT-D.3, WT-D.4, WT-D.5</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7035,7 @@
       </c>
       <c r="G141" s="12" t="inlineStr">
         <is>
-          <t>WT-A.8, WT-D.2, WT-D.3, WT-D.4</t>
+          <t>WT-A.8, WT-D.2, WT-D.3, WT-D.4, WT-D.5</t>
         </is>
       </c>
     </row>
@@ -7061,7 +7070,7 @@
       </c>
       <c r="G142" s="12" t="inlineStr">
         <is>
-          <t>WT-A.8, WT-D.2, WT-D.3, WT-D.4</t>
+          <t>WT-A.8, WT-D.2, WT-D.3, WT-D.4, WT-D.5</t>
         </is>
       </c>
     </row>
@@ -7096,7 +7105,7 @@
       </c>
       <c r="G143" s="12" t="inlineStr">
         <is>
-          <t>WT-A.8, WT-D.2, WT-D.3, WT-D.4</t>
+          <t>WT-A.8, WT-D.2, WT-D.3, WT-D.4, WT-D.5</t>
         </is>
       </c>
     </row>
@@ -7131,7 +7140,7 @@
       </c>
       <c r="G144" s="12" t="inlineStr">
         <is>
-          <t>WT-A.8, WT-D.2, WT-D.3, WT-D.4</t>
+          <t>WT-A.8, WT-D.2, WT-D.3, WT-D.4, WT-D.5</t>
         </is>
       </c>
     </row>
@@ -7446,7 +7455,7 @@
       </c>
       <c r="G153" s="12" t="inlineStr">
         <is>
-          <t>WT-B.4, WT-B.7, WT-C.7, WT-D.1, WT-D.5</t>
+          <t>WT-B.4, WT-B.7, WT-C.7, WT-D.1</t>
         </is>
       </c>
     </row>
@@ -7481,7 +7490,7 @@
       </c>
       <c r="G154" s="12" t="inlineStr">
         <is>
-          <t>WT-B.4, WT-B.7, WT-C.7, WT-D.1, WT-D.5</t>
+          <t>WT-B.4, WT-B.7, WT-C.7, WT-D.1</t>
         </is>
       </c>
     </row>
@@ -7516,7 +7525,7 @@
       </c>
       <c r="G155" s="12" t="inlineStr">
         <is>
-          <t>WT-B.4, WT-B.7, WT-C.7, WT-D.1, WT-D.5</t>
+          <t>WT-B.4, WT-B.7, WT-C.7, WT-D.1</t>
         </is>
       </c>
     </row>
@@ -7551,7 +7560,7 @@
       </c>
       <c r="G156" s="12" t="inlineStr">
         <is>
-          <t>WT-B.4, WT-B.7, WT-C.7, WT-D.1, WT-D.5</t>
+          <t>WT-B.4, WT-B.7, WT-C.7, WT-D.1</t>
         </is>
       </c>
     </row>
@@ -7586,7 +7595,7 @@
       </c>
       <c r="G157" s="12" t="inlineStr">
         <is>
-          <t>WT-B.4, WT-B.7, WT-C.7, WT-D.1, WT-D.5</t>
+          <t>WT-B.4, WT-B.7, WT-C.7, WT-D.1</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7630,7 @@
       </c>
       <c r="G158" s="12" t="inlineStr">
         <is>
-          <t>WT-B.4, WT-B.7, WT-C.7, WT-D.1, WT-D.5</t>
+          <t>WT-B.4, WT-B.7, WT-C.7, WT-D.1</t>
         </is>
       </c>
     </row>
@@ -7656,7 +7665,7 @@
       </c>
       <c r="G159" s="12" t="inlineStr">
         <is>
-          <t>WT-B.4, WT-B.7, WT-C.7, WT-D.1, WT-D.5</t>
+          <t>WT-B.4, WT-B.7, WT-C.7, WT-D.1</t>
         </is>
       </c>
     </row>
@@ -7691,7 +7700,7 @@
       </c>
       <c r="G160" s="12" t="inlineStr">
         <is>
-          <t>WT-B.4, WT-B.7, WT-C.7, WT-D.1, WT-D.5</t>
+          <t>WT-B.4, WT-B.7, WT-C.7, WT-D.1</t>
         </is>
       </c>
     </row>
@@ -7726,7 +7735,7 @@
       </c>
       <c r="G161" s="12" t="inlineStr">
         <is>
-          <t>WT-B.4, WT-B.7, WT-C.7, WT-D.1, WT-D.5</t>
+          <t>WT-B.4, WT-B.7, WT-C.7, WT-D.1</t>
         </is>
       </c>
     </row>
@@ -7761,7 +7770,7 @@
       </c>
       <c r="G162" s="12" t="inlineStr">
         <is>
-          <t>WT-B.4, WT-B.7, WT-C.7, WT-D.1, WT-D.5</t>
+          <t>WT-B.4, WT-B.7, WT-C.7, WT-D.1</t>
         </is>
       </c>
     </row>
@@ -7796,7 +7805,7 @@
       </c>
       <c r="G163" s="12" t="inlineStr">
         <is>
-          <t>WT-B.4, WT-B.7, WT-C.7, WT-D.1, WT-D.5</t>
+          <t>WT-B.4, WT-B.7, WT-C.7, WT-D.1</t>
         </is>
       </c>
     </row>
@@ -7831,7 +7840,7 @@
       </c>
       <c r="G164" s="12" t="inlineStr">
         <is>
-          <t>WT-A.2, WT-A.4, WT-A.8, WT-B.2, WT-B.3, WT-B.5, WT-B.6, WT-B.9, WT-B.10, WT-C.6, WT-C.9, WT-D.2, WT-D.3, WT-D.4</t>
+          <t>WT-A.2, WT-A.4, WT-A.8, WT-B.2, WT-B.3, WT-B.5, WT-B.6, WT-B.9, WT-B.10, WT-C.6, WT-C.9, WT-D.2, WT-D.3, WT-D.4, WT-D.5</t>
         </is>
       </c>
     </row>
@@ -7936,7 +7945,7 @@
       </c>
       <c r="G167" s="12" t="inlineStr">
         <is>
-          <t>WT-A.8, WT-D.2, WT-D.3, WT-D.4</t>
+          <t>WT-A.8, WT-D.2, WT-D.3, WT-D.4, WT-D.5</t>
         </is>
       </c>
     </row>
@@ -8391,7 +8400,7 @@
       </c>
       <c r="G180" s="12" t="inlineStr">
         <is>
-          <t>WT-B.4, WT-B.7, WT-C.7, WT-D.1, WT-D.5</t>
+          <t>WT-B.4, WT-B.7, WT-C.7, WT-D.1</t>
         </is>
       </c>
     </row>
@@ -8496,7 +8505,7 @@
       </c>
       <c r="G183" s="12" t="inlineStr">
         <is>
-          <t>WT-A.7, WT-A.8, WT-B.10, WT-C.11, WT-C.12, WT-C.9, WT-D.2, WT-D.3, WT-D.4</t>
+          <t>WT-A.7, WT-A.8, WT-B.10, WT-C.11, WT-C.12, WT-C.9, WT-D.2, WT-D.3, WT-D.4, WT-D.5</t>
         </is>
       </c>
     </row>
@@ -8706,7 +8715,7 @@
       </c>
       <c r="G189" s="12" t="inlineStr">
         <is>
-          <t>WT-A.8, WT-D.2, WT-D.3, WT-D.4</t>
+          <t>WT-A.8, WT-D.2, WT-D.3, WT-D.4, WT-D.5</t>
         </is>
       </c>
     </row>
@@ -20502,7 +20511,7 @@
       </c>
       <c r="J122" s="12" t="inlineStr">
         <is>
-          <t>TD-UA-01 Test users per role; TD-UA-06 Parameters and jobs as delivered</t>
+          <t>TD-UA-01 Test users per role; TD-UA-06 Parameters and jobs by default</t>
         </is>
       </c>
       <c r="K122" s="12" t="inlineStr">
@@ -20583,7 +20592,7 @@
       </c>
       <c r="J123" s="12" t="inlineStr">
         <is>
-          <t>TD-UA-01 Test users per role; TD-UA-06 Parameters and jobs as delivered</t>
+          <t>TD-UA-01 Test users per role; TD-UA-06 Parameters and jobs by default</t>
         </is>
       </c>
       <c r="K123" s="12" t="inlineStr">
@@ -20664,7 +20673,7 @@
       </c>
       <c r="J124" s="12" t="inlineStr">
         <is>
-          <t>TD-UA-01 Test users per role; TD-UA-06 Parameters and jobs as delivered</t>
+          <t>TD-UA-01 Test users per role; TD-UA-06 Parameters and jobs by default</t>
         </is>
       </c>
       <c r="K124" s="12" t="inlineStr">
@@ -20745,7 +20754,7 @@
       </c>
       <c r="J125" s="12" t="inlineStr">
         <is>
-          <t>TD-UA-01 Test users per role; TD-UA-06 Parameters and jobs as delivered</t>
+          <t>TD-UA-01 Test users per role; TD-UA-06 Parameters and jobs by default</t>
         </is>
       </c>
       <c r="K125" s="12" t="inlineStr">
@@ -20826,7 +20835,7 @@
       </c>
       <c r="J126" s="12" t="inlineStr">
         <is>
-          <t>TD-UA-01 Test users per role; TD-UA-06 Parameters and jobs as delivered</t>
+          <t>TD-UA-01 Test users per role; TD-UA-06 Parameters and jobs by default</t>
         </is>
       </c>
       <c r="K126" s="12" t="inlineStr">
@@ -20907,7 +20916,7 @@
       </c>
       <c r="J127" s="12" t="inlineStr">
         <is>
-          <t>TD-UA-01 Test users per role; TD-UA-06 Parameters and jobs as delivered</t>
+          <t>TD-UA-01 Test users per role; TD-UA-06 Parameters and jobs by default</t>
         </is>
       </c>
       <c r="K127" s="12" t="inlineStr">
@@ -20988,7 +20997,7 @@
       </c>
       <c r="J128" s="12" t="inlineStr">
         <is>
-          <t>TD-UA-01 Test users per role; TD-UA-06 Parameters and jobs as delivered</t>
+          <t>TD-UA-01 Test users per role; TD-UA-06 Parameters and jobs by default</t>
         </is>
       </c>
       <c r="K128" s="12" t="inlineStr">
@@ -21070,7 +21079,7 @@
       </c>
       <c r="J129" s="12" t="inlineStr">
         <is>
-          <t>TD-UA-06 Parameters and jobs as delivered</t>
+          <t>TD-UA-06 Parameters and jobs by default</t>
         </is>
       </c>
       <c r="K129" s="12" t="inlineStr">
@@ -21151,7 +21160,7 @@
       </c>
       <c r="J130" s="12" t="inlineStr">
         <is>
-          <t>TD-UA-06 Parameters and jobs as delivered</t>
+          <t>TD-UA-06 Parameters and jobs by default</t>
         </is>
       </c>
       <c r="K130" s="12" t="inlineStr">
@@ -21232,7 +21241,7 @@
       </c>
       <c r="J131" s="12" t="inlineStr">
         <is>
-          <t>TD-UA-06 Parameters and jobs as delivered</t>
+          <t>TD-UA-06 Parameters and jobs by default</t>
         </is>
       </c>
       <c r="K131" s="12" t="inlineStr">
@@ -21313,7 +21322,7 @@
       </c>
       <c r="J132" s="12" t="inlineStr">
         <is>
-          <t>TD-UA-06 Parameters and jobs as delivered</t>
+          <t>TD-UA-06 Parameters and jobs by default</t>
         </is>
       </c>
       <c r="K132" s="12" t="inlineStr">
@@ -21394,7 +21403,7 @@
       </c>
       <c r="J133" s="12" t="inlineStr">
         <is>
-          <t>TD-UA-06 Parameters and jobs as delivered</t>
+          <t>TD-UA-06 Parameters and jobs by default</t>
         </is>
       </c>
       <c r="K133" s="12" t="inlineStr">
@@ -21476,7 +21485,7 @@
       </c>
       <c r="J134" s="12" t="inlineStr">
         <is>
-          <t>TD-UA-06 Parameters and jobs as delivered</t>
+          <t>TD-UA-06 Parameters and jobs by default</t>
         </is>
       </c>
       <c r="K134" s="12" t="inlineStr">
@@ -21558,7 +21567,7 @@
       </c>
       <c r="J135" s="12" t="inlineStr">
         <is>
-          <t>TD-UA-06 Parameters and jobs as delivered</t>
+          <t>TD-UA-06 Parameters and jobs by default</t>
         </is>
       </c>
       <c r="K135" s="12" t="inlineStr">
@@ -21639,7 +21648,7 @@
       </c>
       <c r="J136" s="12" t="inlineStr">
         <is>
-          <t>TD-UA-06 Parameters and jobs as delivered</t>
+          <t>TD-UA-06 Parameters and jobs by default</t>
         </is>
       </c>
       <c r="K136" s="12" t="inlineStr">
@@ -21722,7 +21731,7 @@
       </c>
       <c r="J137" s="12" t="inlineStr">
         <is>
-          <t>TD-UA-06 Parameters and jobs as delivered; TD-UA-07 Test registration in EIAM</t>
+          <t>TD-UA-06 Parameters and jobs by default; TD-UA-07 Test registration in EIAM</t>
         </is>
       </c>
       <c r="K137" s="12" t="inlineStr">
@@ -21803,7 +21812,7 @@
       </c>
       <c r="J138" s="12" t="inlineStr">
         <is>
-          <t>TD-UA-06 Parameters and jobs as delivered; TD-UA-07 Test registration in EIAM</t>
+          <t>TD-UA-06 Parameters and jobs by default; TD-UA-07 Test registration in EIAM</t>
         </is>
       </c>
       <c r="K138" s="12" t="inlineStr">
@@ -21884,7 +21893,7 @@
       </c>
       <c r="J139" s="12" t="inlineStr">
         <is>
-          <t>TD-UA-06 Parameters and jobs as delivered; TD-UA-07 Test registration in EIAM</t>
+          <t>TD-UA-06 Parameters and jobs by default; TD-UA-07 Test registration in EIAM</t>
         </is>
       </c>
       <c r="K139" s="12" t="inlineStr">
@@ -21965,7 +21974,7 @@
       </c>
       <c r="J140" s="12" t="inlineStr">
         <is>
-          <t>TD-UA-06 Parameters and jobs as delivered; TD-UA-07 Test registration in EIAM</t>
+          <t>TD-UA-06 Parameters and jobs by default; TD-UA-07 Test registration in EIAM</t>
         </is>
       </c>
       <c r="K140" s="12" t="inlineStr">
@@ -22046,12 +22055,12 @@
       </c>
       <c r="J141" s="12" t="inlineStr">
         <is>
-          <t>TD-UA-06 Parameters and jobs as delivered; TD-UA-07 Test registration in EIAM</t>
+          <t>TD-UA-06 Parameters and jobs by default; TD-UA-07 Test registration in EIAM</t>
         </is>
       </c>
       <c r="K141" s="12" t="inlineStr">
         <is>
-          <t>The menu is that of the the system roles of badmin.</t>
+          <t>The menu is that of the system roles of badmin.</t>
         </is>
       </c>
       <c r="L141" s="12" t="inlineStr">
@@ -22128,7 +22137,7 @@
       </c>
       <c r="J142" s="12" t="inlineStr">
         <is>
-          <t>TD-UA-06 Parameters and jobs as delivered; TD-UA-07 Test registration in EIAM</t>
+          <t>TD-UA-06 Parameters and jobs by default; TD-UA-07 Test registration in EIAM</t>
         </is>
       </c>
       <c r="K142" s="12" t="inlineStr">
@@ -22210,7 +22219,7 @@
       </c>
       <c r="J143" s="12" t="inlineStr">
         <is>
-          <t>TD-UA-06 Parameters and jobs as delivered; TD-UA-07 Test registration in EIAM</t>
+          <t>TD-UA-06 Parameters and jobs by default; TD-UA-07 Test registration in EIAM</t>
         </is>
       </c>
       <c r="K143" s="12" t="inlineStr">
@@ -22291,7 +22300,7 @@
       </c>
       <c r="J144" s="12" t="inlineStr">
         <is>
-          <t>TD-UA-06 Parameters and jobs as delivered; TD-UA-07 Test registration in EIAM</t>
+          <t>TD-UA-06 Parameters and jobs by default; TD-UA-07 Test registration in EIAM</t>
         </is>
       </c>
       <c r="K144" s="12" t="inlineStr">
@@ -22372,7 +22381,7 @@
       </c>
       <c r="J145" s="12" t="inlineStr">
         <is>
-          <t>TD-UA-06 Parameters and jobs as delivered; TD-UA-07 Test registration in EIAM</t>
+          <t>TD-UA-06 Parameters and jobs by default; TD-UA-07 Test registration in EIAM</t>
         </is>
       </c>
       <c r="K145" s="12" t="inlineStr">
@@ -22779,7 +22788,7 @@
       </c>
       <c r="J150" s="12" t="inlineStr">
         <is>
-          <t>TD-UA-06 Parameters and jobs as delivered; TD-UA-08 Test mailboxes</t>
+          <t>TD-UA-06 Parameters and jobs by default; TD-UA-08 Test mailboxes</t>
         </is>
       </c>
       <c r="K150" s="12" t="inlineStr">
@@ -22860,7 +22869,7 @@
       </c>
       <c r="J151" s="12" t="inlineStr">
         <is>
-          <t>TD-UA-06 Parameters and jobs as delivered; TD-UA-08 Test mailboxes</t>
+          <t>TD-UA-06 Parameters and jobs by default; TD-UA-08 Test mailboxes</t>
         </is>
       </c>
       <c r="K151" s="12" t="inlineStr">
@@ -22941,7 +22950,7 @@
       </c>
       <c r="J152" s="12" t="inlineStr">
         <is>
-          <t>TD-UA-06 Parameters and jobs as delivered; TD-UA-08 Test mailboxes</t>
+          <t>TD-UA-06 Parameters and jobs by default; TD-UA-08 Test mailboxes</t>
         </is>
       </c>
       <c r="K152" s="12" t="inlineStr">
@@ -23022,7 +23031,7 @@
       </c>
       <c r="J153" s="12" t="inlineStr">
         <is>
-          <t>TD-UA-06 Parameters and jobs as delivered; TD-UA-08 Test mailboxes</t>
+          <t>TD-UA-06 Parameters and jobs by default; TD-UA-08 Test mailboxes</t>
         </is>
       </c>
       <c r="K153" s="12" t="inlineStr">
@@ -23103,7 +23112,7 @@
       </c>
       <c r="J154" s="12" t="inlineStr">
         <is>
-          <t>TD-UA-06 Parameters and jobs as delivered; TD-UA-08 Test mailboxes</t>
+          <t>TD-UA-06 Parameters and jobs by default; TD-UA-08 Test mailboxes</t>
         </is>
       </c>
       <c r="K154" s="12" t="inlineStr">
@@ -23185,7 +23194,7 @@
       </c>
       <c r="J155" s="12" t="inlineStr">
         <is>
-          <t>TD-UA-06 Parameters and jobs as delivered; TD-UA-08 Test mailboxes</t>
+          <t>TD-UA-06 Parameters and jobs by default; TD-UA-08 Test mailboxes</t>
         </is>
       </c>
       <c r="K155" s="12" t="inlineStr">
@@ -23266,7 +23275,7 @@
       </c>
       <c r="J156" s="12" t="inlineStr">
         <is>
-          <t>TD-UA-06 Parameters and jobs as delivered; TD-UA-08 Test mailboxes</t>
+          <t>TD-UA-06 Parameters and jobs by default; TD-UA-08 Test mailboxes</t>
         </is>
       </c>
       <c r="K156" s="12" t="inlineStr">
@@ -23348,7 +23357,7 @@
       </c>
       <c r="J157" s="12" t="inlineStr">
         <is>
-          <t>TD-UA-06 Parameters and jobs as delivered; TD-UA-08 Test mailboxes</t>
+          <t>TD-UA-06 Parameters and jobs by default; TD-UA-08 Test mailboxes</t>
         </is>
       </c>
       <c r="K157" s="12" t="inlineStr">
@@ -23429,7 +23438,7 @@
       </c>
       <c r="J158" s="12" t="inlineStr">
         <is>
-          <t>TD-UA-06 Parameters and jobs as delivered; TD-UA-08 Test mailboxes</t>
+          <t>TD-UA-06 Parameters and jobs by default; TD-UA-08 Test mailboxes</t>
         </is>
       </c>
       <c r="K158" s="12" t="inlineStr">
@@ -23510,7 +23519,7 @@
       </c>
       <c r="J159" s="12" t="inlineStr">
         <is>
-          <t>TD-UA-06 Parameters and jobs as delivered; TD-UA-08 Test mailboxes</t>
+          <t>TD-UA-06 Parameters and jobs by default; TD-UA-08 Test mailboxes</t>
         </is>
       </c>
       <c r="K159" s="12" t="inlineStr">
@@ -23592,7 +23601,7 @@
       </c>
       <c r="J160" s="12" t="inlineStr">
         <is>
-          <t>TD-UA-01 Test users per role; TD-UA-06 Parameters and jobs as delivered</t>
+          <t>TD-UA-01 Test users per role; TD-UA-06 Parameters and jobs by default</t>
         </is>
       </c>
       <c r="K160" s="12" t="inlineStr">
@@ -23673,7 +23682,7 @@
       </c>
       <c r="J161" s="12" t="inlineStr">
         <is>
-          <t>TD-UA-01 Test users per role; TD-UA-06 Parameters and jobs as delivered</t>
+          <t>TD-UA-01 Test users per role; TD-UA-06 Parameters and jobs by default</t>
         </is>
       </c>
       <c r="K161" s="12" t="inlineStr">
@@ -23754,7 +23763,7 @@
       </c>
       <c r="J162" s="12" t="inlineStr">
         <is>
-          <t>TD-UA-01 Test users per role; TD-UA-06 Parameters and jobs as delivered</t>
+          <t>TD-UA-01 Test users per role; TD-UA-06 Parameters and jobs by default</t>
         </is>
       </c>
       <c r="K162" s="12" t="inlineStr">
@@ -28058,7 +28067,7 @@
       </c>
       <c r="J215" s="12" t="inlineStr">
         <is>
-          <t>TD-UA-06 Parameters and jobs as delivered</t>
+          <t>TD-UA-06 Parameters and jobs by default</t>
         </is>
       </c>
       <c r="K215" s="12" t="inlineStr">
@@ -28139,7 +28148,7 @@
       </c>
       <c r="J216" s="12" t="inlineStr">
         <is>
-          <t>TD-UA-06 Parameters and jobs as delivered</t>
+          <t>TD-UA-06 Parameters and jobs by default</t>
         </is>
       </c>
       <c r="K216" s="12" t="inlineStr">
@@ -28220,7 +28229,7 @@
       </c>
       <c r="J217" s="12" t="inlineStr">
         <is>
-          <t>TD-UA-06 Parameters and jobs as delivered</t>
+          <t>TD-UA-06 Parameters and jobs by default</t>
         </is>
       </c>
       <c r="K217" s="12" t="inlineStr">
@@ -28301,7 +28310,7 @@
       </c>
       <c r="J218" s="12" t="inlineStr">
         <is>
-          <t>TD-UA-06 Parameters and jobs as delivered</t>
+          <t>TD-UA-06 Parameters and jobs by default</t>
         </is>
       </c>
       <c r="K218" s="12" t="inlineStr">
@@ -29356,7 +29365,7 @@
       </c>
       <c r="J231" s="12" t="inlineStr">
         <is>
-          <t>TD-UA-03 Group profiles; TD-UA-06 Parameters and jobs as delivered</t>
+          <t>TD-UA-03 Group profiles; TD-UA-06 Parameters and jobs by default</t>
         </is>
       </c>
       <c r="K231" s="12" t="inlineStr">
@@ -29437,7 +29446,7 @@
       </c>
       <c r="J232" s="12" t="inlineStr">
         <is>
-          <t>TD-UA-03 Group profiles; TD-UA-06 Parameters and jobs as delivered</t>
+          <t>TD-UA-03 Group profiles; TD-UA-06 Parameters and jobs by default</t>
         </is>
       </c>
       <c r="K232" s="12" t="inlineStr">
@@ -29518,7 +29527,7 @@
       </c>
       <c r="J233" s="12" t="inlineStr">
         <is>
-          <t>TD-UA-03 Group profiles; TD-UA-06 Parameters and jobs as delivered</t>
+          <t>TD-UA-03 Group profiles; TD-UA-06 Parameters and jobs by default</t>
         </is>
       </c>
       <c r="K233" s="12" t="inlineStr">
@@ -29599,7 +29608,7 @@
       </c>
       <c r="J234" s="12" t="inlineStr">
         <is>
-          <t>TD-UA-03 Group profiles; TD-UA-06 Parameters and jobs as delivered</t>
+          <t>TD-UA-03 Group profiles; TD-UA-06 Parameters and jobs by default</t>
         </is>
       </c>
       <c r="K234" s="12" t="inlineStr">
@@ -29680,7 +29689,7 @@
       </c>
       <c r="J235" s="12" t="inlineStr">
         <is>
-          <t>TD-UA-03 Group profiles; TD-UA-06 Parameters and jobs as delivered</t>
+          <t>TD-UA-03 Group profiles; TD-UA-06 Parameters and jobs by default</t>
         </is>
       </c>
       <c r="K235" s="12" t="inlineStr">
@@ -33334,7 +33343,7 @@
       </c>
       <c r="J280" s="12" t="inlineStr">
         <is>
-          <t>TD-UA-06 Parameters and jobs as delivered</t>
+          <t>TD-UA-06 Parameters and jobs by default</t>
         </is>
       </c>
       <c r="K280" s="12" t="inlineStr">
@@ -33415,7 +33424,7 @@
       </c>
       <c r="J281" s="12" t="inlineStr">
         <is>
-          <t>TD-UA-06 Parameters and jobs as delivered</t>
+          <t>TD-UA-06 Parameters and jobs by default</t>
         </is>
       </c>
       <c r="K281" s="12" t="inlineStr">
@@ -33496,7 +33505,7 @@
       </c>
       <c r="J282" s="12" t="inlineStr">
         <is>
-          <t>TD-UA-06 Parameters and jobs as delivered</t>
+          <t>TD-UA-06 Parameters and jobs by default</t>
         </is>
       </c>
       <c r="K282" s="12" t="inlineStr">
@@ -33577,7 +33586,7 @@
       </c>
       <c r="J283" s="12" t="inlineStr">
         <is>
-          <t>TD-UA-06 Parameters and jobs as delivered</t>
+          <t>TD-UA-06 Parameters and jobs by default</t>
         </is>
       </c>
       <c r="K283" s="12" t="inlineStr">
@@ -33658,7 +33667,7 @@
       </c>
       <c r="J284" s="12" t="inlineStr">
         <is>
-          <t>TD-UA-06 Parameters and jobs as delivered</t>
+          <t>TD-UA-06 Parameters and jobs by default</t>
         </is>
       </c>
       <c r="K284" s="12" t="inlineStr">
@@ -35359,7 +35368,7 @@
       </c>
       <c r="J305" s="12" t="inlineStr">
         <is>
-          <t>TD-UA-06 Parameters and jobs as delivered; TD-UA-08 Test mailboxes</t>
+          <t>TD-UA-06 Parameters and jobs by default; TD-UA-08 Test mailboxes</t>
         </is>
       </c>
       <c r="K305" s="12" t="inlineStr">
@@ -35440,7 +35449,7 @@
       </c>
       <c r="J306" s="12" t="inlineStr">
         <is>
-          <t>TD-UA-06 Parameters and jobs as delivered; TD-UA-08 Test mailboxes</t>
+          <t>TD-UA-06 Parameters and jobs by default; TD-UA-08 Test mailboxes</t>
         </is>
       </c>
       <c r="K306" s="12" t="inlineStr">
@@ -35521,7 +35530,7 @@
       </c>
       <c r="J307" s="12" t="inlineStr">
         <is>
-          <t>TD-UA-06 Parameters and jobs as delivered; TD-UA-08 Test mailboxes</t>
+          <t>TD-UA-06 Parameters and jobs by default; TD-UA-08 Test mailboxes</t>
         </is>
       </c>
       <c r="K307" s="12" t="inlineStr">
@@ -37338,7 +37347,7 @@
       </c>
       <c r="B41" s="12" t="inlineStr">
         <is>
-          <t>Matching the EIAM account to the the system user: BDOI IT to confirm the claim that identifies the user and the relation of the Windows ID to the user ID (UA-Q08, UA-Q25).</t>
+          <t>Matching the EIAM account to the system user: BDOI IT to confirm the claim that identifies the user and the relation of the Windows ID to the user ID (UA-Q08, UA-Q25).</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
@@ -37365,7 +37374,7 @@
       </c>
       <c r="B42" s="12" t="inlineStr">
         <is>
-          <t>Which claim identifies the user returned by EIAM: the Windows ID (on-premises account name), the user principal name (UPN), or the employee number? Please also give the format of the Windows ID and how it relates to the the system user ID (a999999999)..</t>
+          <t>Which claim identifies the user returned by EIAM: the Windows ID (on-premises account name), the user principal name (UPN), or the employee number? Please also give the format of the Windows ID and how it relates to the system user ID (a999999999)..</t>
         </is>
       </c>
       <c r="C42" s="12" t="inlineStr">

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-11_User_Access_Maintenance/BIBS_RTM_BRD-11_Test_Cases_and_Traceability_v1.1.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-11_User_Access_Maintenance/BIBS_RTM_BRD-11_Test_Cases_and_Traceability_v1.1.xlsx
@@ -1033,7 +1033,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Test Cases and Traceability&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Test Cases and Traceability&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.1</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -1133,7 +1133,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Test Cases and Traceability&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Test Cases and Traceability&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.1</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -1975,7 +1975,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Test Cases and Traceability&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Test Cases and Traceability&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.1</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -2156,7 +2156,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Test Cases and Traceability&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Test Cases and Traceability&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.1</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -8733,7 +8733,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Test Cases and Traceability&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Test Cases and Traceability&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.1</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -10716,7 +10716,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Test Cases and Traceability&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Test Cases and Traceability&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.1</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -22096,7 +22096,7 @@
       </c>
       <c r="B142" s="12" t="inlineStr">
         <is>
-          <t>Joiner and leaver from the Enterprise SSO simulator</t>
+          <t>Joiner and leaver from the Enterprise SSO test accounts</t>
         </is>
       </c>
       <c r="C142" s="12" t="inlineStr">
@@ -22126,12 +22126,12 @@
       </c>
       <c r="H142" s="12" t="inlineStr">
         <is>
-          <t>Enterprise SSO simulator of the SIT and UAT environment; setting Users from the Enterprise SSO platform on.</t>
+          <t>Test accounts of BDOI's Enterprise SSO provided under the Integration scope for SIT and UAT; setting Users from the Enterprise SSO platform on.</t>
         </is>
       </c>
       <c r="I142" s="12" t="inlineStr">
         <is>
-          <t>1. On Identity Synchronisation › Enterprise SSO Simulator add the account BDO\uat.joiner with user ID a013000195 and send joiner.
+          <t>1. With the Enterprise SSO test accounts provided under the Integration scope, set up the account BDO\uat.joiner with user ID a013000195 and send joiner.
 2. Change the account to the AD status Disabled and send status change.</t>
         </is>
       </c>
@@ -22214,7 +22214,7 @@
       <c r="I143" s="12" t="inlineStr">
         <is>
           <t>1. Send a joiner of an account whose Windows ID belongs to another user.
-2. Open the bell; correct the account in the simulator; on Events choose Process again.</t>
+2. Open the bell; correct the account in the Enterprise SSO test accounts; on Events choose Process again.</t>
         </is>
       </c>
       <c r="J143" s="12" t="inlineStr">
@@ -35599,7 +35599,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Test Cases and Traceability&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Test Cases and Traceability&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.1</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -36293,7 +36293,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Test Cases and Traceability&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Test Cases and Traceability&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.1</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -37569,7 +37569,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Test Cases and Traceability&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Test Cases and Traceability&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.1</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -37793,7 +37793,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Test Cases and Traceability&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Test Cases and Traceability&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.1</oddFooter>
     <evenHeader/>
     <evenFooter/>

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-11_User_Access_Maintenance/BIBS_RTM_BRD-11_Test_Cases_and_Traceability_v1.1.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-11_User_Access_Maintenance/BIBS_RTM_BRD-11_Test_Cases_and_Traceability_v1.1.xlsx
@@ -35597,7 +35597,7 @@
   </dataValidations>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;8 &amp;K004EA8Test Cases and Traceability&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.1</oddFooter>

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-11_User_Access_Maintenance/BIBS_RTM_BRD-11_Test_Cases_and_Traceability_v1.1.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-11_User_Access_Maintenance/BIBS_RTM_BRD-11_Test_Cases_and_Traceability_v1.1.xlsx
@@ -806,7 +806,7 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>11 October 2026</t>
+          <t>13 October 2026</t>
         </is>
       </c>
     </row>
@@ -1543,12 +1543,12 @@
       </c>
       <c r="B27" s="20" t="inlineStr">
         <is>
-          <t>Sign-in ID</t>
+          <t>User (FRS Annex O)</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>The password is issued separately by the iorta TechNXT Project Team</t>
+          <t>Fictitious user of the persona (FRS Annex O)</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr"/>
@@ -10740,7 +10740,7 @@
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="30" customWidth="1" min="8" max="8"/>
     <col width="50" customWidth="1" min="9" max="9"/>
@@ -10819,7 +10819,7 @@
       </c>
       <c r="F4" s="24" t="inlineStr">
         <is>
-          <t>Sign-in ID</t>
+          <t>User (FRS Annex O)</t>
         </is>
       </c>
       <c r="G4" s="24" t="inlineStr">
@@ -10916,7 +10916,7 @@
       </c>
       <c r="F5" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G5" s="12" t="inlineStr">
@@ -10926,12 +10926,12 @@
       </c>
       <c r="H5" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I5" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as requestor (Requestor).
+          <t>1. Sign in as Rhea Santiago (Requestor).
 2. Open Login page; any screen.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -10999,7 +10999,7 @@
       </c>
       <c r="F6" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G6" s="12" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="H6" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I6" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as requestor (Requestor).
+          <t>1. Sign in as Rhea Santiago (Requestor).
 2. Open Login page; any screen.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -11082,7 +11082,7 @@
       </c>
       <c r="F7" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G7" s="12" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="H7" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I7" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as requestor (Requestor).
+          <t>1. Sign in as Rhea Santiago (Requestor).
 2. Open Login page; any screen.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -11165,7 +11165,7 @@
       </c>
       <c r="F8" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G8" s="12" t="inlineStr">
@@ -11175,12 +11175,12 @@
       </c>
       <c r="H8" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I8" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as requestor (Requestor).
+          <t>1. Sign in as Rhea Santiago (Requestor).
 2. Open Login page; any screen.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -11248,7 +11248,7 @@
       </c>
       <c r="F9" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G9" s="12" t="inlineStr">
@@ -11258,12 +11258,12 @@
       </c>
       <c r="H9" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I9" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as requestor (Requestor).
+          <t>1. Sign in as Rhea Santiago (Requestor).
 2. Open Login page; any screen.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -11331,7 +11331,7 @@
       </c>
       <c r="F10" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G10" s="12" t="inlineStr">
@@ -11341,12 +11341,12 @@
       </c>
       <c r="H10" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I10" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as requestor (Requestor).
+          <t>1. Sign in as Rhea Santiago (Requestor).
 2. Open Login page; any screen.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -11414,7 +11414,7 @@
       </c>
       <c r="F11" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G11" s="12" t="inlineStr">
@@ -11424,12 +11424,12 @@
       </c>
       <c r="H11" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I11" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as requestor (Requestor).
+          <t>1. Sign in as Rhea Santiago (Requestor).
 2. Open Login page; any screen.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -11497,7 +11497,7 @@
       </c>
       <c r="F12" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G12" s="12" t="inlineStr">
@@ -11507,12 +11507,12 @@
       </c>
       <c r="H12" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I12" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as requestor (Requestor).
+          <t>1. Sign in as Rhea Santiago (Requestor).
 2. Open Login page; any screen.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -11580,7 +11580,7 @@
       </c>
       <c r="F13" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G13" s="12" t="inlineStr">
@@ -11590,12 +11590,12 @@
       </c>
       <c r="H13" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I13" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as requestor (Requestor).
+          <t>1. Sign in as Rhea Santiago (Requestor).
 2. Open Login page; any screen.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -11663,7 +11663,7 @@
       </c>
       <c r="F14" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G14" s="12" t="inlineStr">
@@ -11673,12 +11673,12 @@
       </c>
       <c r="H14" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I14" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as requestor (Requestor).
+          <t>1. Sign in as Rhea Santiago (Requestor).
 2. Open Login page; any screen.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -11746,7 +11746,7 @@
       </c>
       <c r="F15" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G15" s="12" t="inlineStr">
@@ -11756,12 +11756,12 @@
       </c>
       <c r="H15" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I15" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as requestor (Requestor).
+          <t>1. Sign in as Rhea Santiago (Requestor).
 2. Open Login page; any screen.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -11829,7 +11829,7 @@
       </c>
       <c r="F16" s="12" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>Samuel Cruz</t>
         </is>
       </c>
       <c r="G16" s="12" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="H16" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I16" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as admin (System Administrator).
+          <t>1. Sign in as Samuel Cruz (System Administrator).
 2. Open Administration › Users.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -11856,7 +11856,7 @@
       </c>
       <c r="K16" s="12" t="inlineStr">
         <is>
-          <t>An enrolment of user a013000196 with the profile Marketing Account Officer, approved by another user, creates the user, who can then sign in.</t>
+          <t>An enrolment of user Isabel Navarro with the profile Marketing Account Officer, approved by another user, creates the user, who can then sign in.</t>
         </is>
       </c>
       <c r="L16" s="12" t="inlineStr">
@@ -11912,7 +11912,7 @@
       </c>
       <c r="F17" s="12" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>Samuel Cruz</t>
         </is>
       </c>
       <c r="G17" s="12" t="inlineStr">
@@ -11922,12 +11922,12 @@
       </c>
       <c r="H17" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I17" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as admin (System Administrator).
+          <t>1. Sign in as Samuel Cruz (System Administrator).
 2. Open Administration › Users.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -11939,7 +11939,7 @@
       </c>
       <c r="K17" s="12" t="inlineStr">
         <is>
-          <t>An enrolment with an existing user ID is refused with "User a013000196 already exists".</t>
+          <t>An enrolment with an existing user ID is refused with "User Isabel Navarro already exists".</t>
         </is>
       </c>
       <c r="L17" s="12" t="inlineStr">
@@ -11995,7 +11995,7 @@
       </c>
       <c r="F18" s="12" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>Samuel Cruz</t>
         </is>
       </c>
       <c r="G18" s="12" t="inlineStr">
@@ -12005,12 +12005,12 @@
       </c>
       <c r="H18" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I18" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as admin (System Administrator).
+          <t>1. Sign in as Samuel Cruz (System Administrator).
 2. Open Administration › Users.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -12078,7 +12078,7 @@
       </c>
       <c r="F19" s="12" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>Samuel Cruz</t>
         </is>
       </c>
       <c r="G19" s="12" t="inlineStr">
@@ -12088,12 +12088,12 @@
       </c>
       <c r="H19" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I19" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as admin (System Administrator).
+          <t>1. Sign in as Samuel Cruz (System Administrator).
 2. Open Administration › Users.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -12157,7 +12157,7 @@
       </c>
       <c r="F20" s="12" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>Samuel Cruz</t>
         </is>
       </c>
       <c r="G20" s="12" t="inlineStr">
@@ -12167,12 +12167,12 @@
       </c>
       <c r="H20" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I20" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as admin (System Administrator).
+          <t>1. Sign in as Samuel Cruz (System Administrator).
 2. Open Administration › Users.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -12236,7 +12236,7 @@
       </c>
       <c r="F21" s="12" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>Samuel Cruz</t>
         </is>
       </c>
       <c r="G21" s="12" t="inlineStr">
@@ -12246,12 +12246,12 @@
       </c>
       <c r="H21" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I21" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as admin (System Administrator).
+          <t>1. Sign in as Samuel Cruz (System Administrator).
 2. Open Administration › Users.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -12319,7 +12319,7 @@
       </c>
       <c r="F22" s="12" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>Samuel Cruz</t>
         </is>
       </c>
       <c r="G22" s="12" t="inlineStr">
@@ -12329,12 +12329,12 @@
       </c>
       <c r="H22" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I22" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as admin (System Administrator).
+          <t>1. Sign in as Samuel Cruz (System Administrator).
 2. Open Administration › Users; Access Requests.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -12402,7 +12402,7 @@
       </c>
       <c r="F23" s="12" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>Samuel Cruz</t>
         </is>
       </c>
       <c r="G23" s="12" t="inlineStr">
@@ -12412,12 +12412,12 @@
       </c>
       <c r="H23" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I23" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as admin (System Administrator).
+          <t>1. Sign in as Samuel Cruz (System Administrator).
 2. Open Administration › Users; Access Requests.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -12485,7 +12485,7 @@
       </c>
       <c r="F24" s="12" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>Samuel Cruz</t>
         </is>
       </c>
       <c r="G24" s="12" t="inlineStr">
@@ -12495,12 +12495,12 @@
       </c>
       <c r="H24" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I24" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as admin (System Administrator).
+          <t>1. Sign in as Samuel Cruz (System Administrator).
 2. Open Administration › Users; Access Requests.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -12568,7 +12568,7 @@
       </c>
       <c r="F25" s="12" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>Samuel Cruz</t>
         </is>
       </c>
       <c r="G25" s="12" t="inlineStr">
@@ -12578,12 +12578,12 @@
       </c>
       <c r="H25" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I25" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as admin (System Administrator).
+          <t>1. Sign in as Samuel Cruz (System Administrator).
 2. Open Administration › Users; Access Requests.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -12651,7 +12651,7 @@
       </c>
       <c r="F26" s="12" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>Samuel Cruz</t>
         </is>
       </c>
       <c r="G26" s="12" t="inlineStr">
@@ -12661,12 +12661,12 @@
       </c>
       <c r="H26" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I26" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as admin (System Administrator).
+          <t>1. Sign in as Samuel Cruz (System Administrator).
 2. Open Administration › Users; Access Requests.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -12734,7 +12734,7 @@
       </c>
       <c r="F27" s="12" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>Samuel Cruz</t>
         </is>
       </c>
       <c r="G27" s="12" t="inlineStr">
@@ -12744,12 +12744,12 @@
       </c>
       <c r="H27" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I27" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as admin (System Administrator).
+          <t>1. Sign in as Samuel Cruz (System Administrator).
 2. Open Administration › Users; Access Requests.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -12817,7 +12817,7 @@
       </c>
       <c r="F28" s="12" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>Samuel Cruz</t>
         </is>
       </c>
       <c r="G28" s="12" t="inlineStr">
@@ -12827,12 +12827,12 @@
       </c>
       <c r="H28" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I28" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as admin (System Administrator).
+          <t>1. Sign in as Samuel Cruz (System Administrator).
 2. Open Administration › Users; Access Requests.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -12896,7 +12896,7 @@
       </c>
       <c r="F29" s="12" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>Samuel Cruz</t>
         </is>
       </c>
       <c r="G29" s="12" t="inlineStr">
@@ -12906,12 +12906,12 @@
       </c>
       <c r="H29" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I29" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as admin (System Administrator).
+          <t>1. Sign in as Samuel Cruz (System Administrator).
 2. Open Administration › Users; Access Requests.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -12975,7 +12975,7 @@
       </c>
       <c r="F30" s="12" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>Samuel Cruz</t>
         </is>
       </c>
       <c r="G30" s="12" t="inlineStr">
@@ -12985,12 +12985,12 @@
       </c>
       <c r="H30" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I30" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as admin (System Administrator).
+          <t>1. Sign in as Samuel Cruz (System Administrator).
 2. Open Administration › Users; Access Requests.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="F31" s="12" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>Samuel Cruz</t>
         </is>
       </c>
       <c r="G31" s="12" t="inlineStr">
@@ -13064,12 +13064,12 @@
       </c>
       <c r="H31" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I31" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as admin (System Administrator).
+          <t>1. Sign in as Samuel Cruz (System Administrator).
 2. Open Login page; My Profile.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -13133,7 +13133,7 @@
       </c>
       <c r="F32" s="12" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>Samuel Cruz</t>
         </is>
       </c>
       <c r="G32" s="12" t="inlineStr">
@@ -13143,12 +13143,12 @@
       </c>
       <c r="H32" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I32" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as admin (System Administrator).
+          <t>1. Sign in as Samuel Cruz (System Administrator).
 2. Open Login page; My Profile.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -13212,7 +13212,7 @@
       </c>
       <c r="F33" s="12" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>Samuel Cruz</t>
         </is>
       </c>
       <c r="G33" s="12" t="inlineStr">
@@ -13222,12 +13222,12 @@
       </c>
       <c r="H33" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I33" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as admin (System Administrator).
+          <t>1. Sign in as Samuel Cruz (System Administrator).
 2. Open Login page; My Profile.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -13291,7 +13291,7 @@
       </c>
       <c r="F34" s="12" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>Samuel Cruz</t>
         </is>
       </c>
       <c r="G34" s="12" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="H34" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I34" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as admin (System Administrator).
+          <t>1. Sign in as Samuel Cruz (System Administrator).
 2. Open Login page; My Profile.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -13370,7 +13370,7 @@
       </c>
       <c r="F35" s="12" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>Samuel Cruz</t>
         </is>
       </c>
       <c r="G35" s="12" t="inlineStr">
@@ -13380,12 +13380,12 @@
       </c>
       <c r="H35" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I35" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as admin (System Administrator).
+          <t>1. Sign in as Samuel Cruz (System Administrator).
 2. Open Login page; My Profile.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -13449,7 +13449,7 @@
       </c>
       <c r="F36" s="12" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>Samuel Cruz</t>
         </is>
       </c>
       <c r="G36" s="12" t="inlineStr">
@@ -13459,12 +13459,12 @@
       </c>
       <c r="H36" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I36" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as admin (System Administrator).
+          <t>1. Sign in as Samuel Cruz (System Administrator).
 2. Open Login page; My Profile.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -13532,7 +13532,7 @@
       </c>
       <c r="F37" s="12" t="inlineStr">
         <is>
-          <t>badmin</t>
+          <t>Bea Villanueva</t>
         </is>
       </c>
       <c r="G37" s="12" t="inlineStr">
@@ -13542,12 +13542,12 @@
       </c>
       <c r="H37" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I37" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as badmin (Business Administrator).
+          <t>1. Sign in as Bea Villanueva (Business Administrator).
 2. Open User Access › Group Profile Requests; Roles &amp; Permissions.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -13615,7 +13615,7 @@
       </c>
       <c r="F38" s="12" t="inlineStr">
         <is>
-          <t>badmin</t>
+          <t>Bea Villanueva</t>
         </is>
       </c>
       <c r="G38" s="12" t="inlineStr">
@@ -13625,12 +13625,12 @@
       </c>
       <c r="H38" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I38" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as badmin (Business Administrator).
+          <t>1. Sign in as Bea Villanueva (Business Administrator).
 2. Open User Access › Group Profile Requests; Roles &amp; Permissions.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -13698,7 +13698,7 @@
       </c>
       <c r="F39" s="12" t="inlineStr">
         <is>
-          <t>badmin</t>
+          <t>Bea Villanueva</t>
         </is>
       </c>
       <c r="G39" s="12" t="inlineStr">
@@ -13708,12 +13708,12 @@
       </c>
       <c r="H39" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I39" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as badmin (Business Administrator).
+          <t>1. Sign in as Bea Villanueva (Business Administrator).
 2. Open User Access › Group Profile Requests; Roles &amp; Permissions.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -13781,7 +13781,7 @@
       </c>
       <c r="F40" s="12" t="inlineStr">
         <is>
-          <t>badmin</t>
+          <t>Bea Villanueva</t>
         </is>
       </c>
       <c r="G40" s="12" t="inlineStr">
@@ -13791,12 +13791,12 @@
       </c>
       <c r="H40" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I40" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as badmin (Business Administrator).
+          <t>1. Sign in as Bea Villanueva (Business Administrator).
 2. Open User Access › Group Profile Requests.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -13864,7 +13864,7 @@
       </c>
       <c r="F41" s="12" t="inlineStr">
         <is>
-          <t>badmin</t>
+          <t>Bea Villanueva</t>
         </is>
       </c>
       <c r="G41" s="12" t="inlineStr">
@@ -13874,12 +13874,12 @@
       </c>
       <c r="H41" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I41" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as badmin (Business Administrator).
+          <t>1. Sign in as Bea Villanueva (Business Administrator).
 2. Open User Access › Group Profile Requests.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -13947,7 +13947,7 @@
       </c>
       <c r="F42" s="12" t="inlineStr">
         <is>
-          <t>badmin</t>
+          <t>Bea Villanueva</t>
         </is>
       </c>
       <c r="G42" s="12" t="inlineStr">
@@ -13957,12 +13957,12 @@
       </c>
       <c r="H42" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I42" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as badmin (Business Administrator).
+          <t>1. Sign in as Bea Villanueva (Business Administrator).
 2. Open User Access › Group Profile Requests.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -14030,7 +14030,7 @@
       </c>
       <c r="F43" s="12" t="inlineStr">
         <is>
-          <t>badmin</t>
+          <t>Bea Villanueva</t>
         </is>
       </c>
       <c r="G43" s="12" t="inlineStr">
@@ -14040,12 +14040,12 @@
       </c>
       <c r="H43" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I43" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as badmin (Business Administrator).
+          <t>1. Sign in as Bea Villanueva (Business Administrator).
 2. Open User Access › Group Profile Requests.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -14113,7 +14113,7 @@
       </c>
       <c r="F44" s="12" t="inlineStr">
         <is>
-          <t>badmin</t>
+          <t>Bea Villanueva</t>
         </is>
       </c>
       <c r="G44" s="12" t="inlineStr">
@@ -14123,12 +14123,12 @@
       </c>
       <c r="H44" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I44" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as badmin (Business Administrator).
+          <t>1. Sign in as Bea Villanueva (Business Administrator).
 2. Open User Access › Group Profile Requests.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -14196,7 +14196,7 @@
       </c>
       <c r="F45" s="12" t="inlineStr">
         <is>
-          <t>badmin</t>
+          <t>Bea Villanueva</t>
         </is>
       </c>
       <c r="G45" s="12" t="inlineStr">
@@ -14206,12 +14206,12 @@
       </c>
       <c r="H45" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I45" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as badmin (Business Administrator).
+          <t>1. Sign in as Bea Villanueva (Business Administrator).
 2. Open User Access › Group Profile Requests.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -14279,7 +14279,7 @@
       </c>
       <c r="F46" s="12" t="inlineStr">
         <is>
-          <t>badmin</t>
+          <t>Bea Villanueva</t>
         </is>
       </c>
       <c r="G46" s="12" t="inlineStr">
@@ -14289,12 +14289,12 @@
       </c>
       <c r="H46" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I46" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as badmin (Business Administrator).
+          <t>1. Sign in as Bea Villanueva (Business Administrator).
 2. Open User Access › Group Profile Requests.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -14362,7 +14362,7 @@
       </c>
       <c r="F47" s="12" t="inlineStr">
         <is>
-          <t>auditor</t>
+          <t>Audrey Lim</t>
         </is>
       </c>
       <c r="G47" s="12" t="inlineStr">
@@ -14372,12 +14372,12 @@
       </c>
       <c r="H47" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I47" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as auditor (Auditor).
+          <t>1. Sign in as Audrey Lim (Auditor).
 2. Open User Access › User Access Reports.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -14445,7 +14445,7 @@
       </c>
       <c r="F48" s="12" t="inlineStr">
         <is>
-          <t>auditor</t>
+          <t>Audrey Lim</t>
         </is>
       </c>
       <c r="G48" s="12" t="inlineStr">
@@ -14455,12 +14455,12 @@
       </c>
       <c r="H48" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I48" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as auditor (Auditor).
+          <t>1. Sign in as Audrey Lim (Auditor).
 2. Open User Access › User Access Reports.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -14528,7 +14528,7 @@
       </c>
       <c r="F49" s="12" t="inlineStr">
         <is>
-          <t>auditor</t>
+          <t>Audrey Lim</t>
         </is>
       </c>
       <c r="G49" s="12" t="inlineStr">
@@ -14538,12 +14538,12 @@
       </c>
       <c r="H49" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I49" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as auditor (Auditor).
+          <t>1. Sign in as Audrey Lim (Auditor).
 2. Open User Access › User Access Reports.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -14611,7 +14611,7 @@
       </c>
       <c r="F50" s="12" t="inlineStr">
         <is>
-          <t>auditor</t>
+          <t>Audrey Lim</t>
         </is>
       </c>
       <c r="G50" s="12" t="inlineStr">
@@ -14621,12 +14621,12 @@
       </c>
       <c r="H50" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I50" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as auditor (Auditor).
+          <t>1. Sign in as Audrey Lim (Auditor).
 2. Open User Access › User Access Reports.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -14690,7 +14690,7 @@
       </c>
       <c r="F51" s="12" t="inlineStr">
         <is>
-          <t>auditor</t>
+          <t>Audrey Lim</t>
         </is>
       </c>
       <c r="G51" s="12" t="inlineStr">
@@ -14700,12 +14700,12 @@
       </c>
       <c r="H51" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I51" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as auditor (Auditor).
+          <t>1. Sign in as Audrey Lim (Auditor).
 2. Open User Access Reports › User Access Audit Log; Audit Trail.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -14769,7 +14769,7 @@
       </c>
       <c r="F52" s="12" t="inlineStr">
         <is>
-          <t>auditor</t>
+          <t>Audrey Lim</t>
         </is>
       </c>
       <c r="G52" s="12" t="inlineStr">
@@ -14779,12 +14779,12 @@
       </c>
       <c r="H52" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I52" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as auditor (Auditor).
+          <t>1. Sign in as Audrey Lim (Auditor).
 2. Open User Access Reports › User Access Audit Log; Audit Trail.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -14848,7 +14848,7 @@
       </c>
       <c r="F53" s="12" t="inlineStr">
         <is>
-          <t>auditor</t>
+          <t>Audrey Lim</t>
         </is>
       </c>
       <c r="G53" s="12" t="inlineStr">
@@ -14858,12 +14858,12 @@
       </c>
       <c r="H53" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I53" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as auditor (Auditor).
+          <t>1. Sign in as Audrey Lim (Auditor).
 2. Open User Access Reports › User Access Audit Log; Audit Trail.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -14927,7 +14927,7 @@
       </c>
       <c r="F54" s="12" t="inlineStr">
         <is>
-          <t>auditor</t>
+          <t>Audrey Lim</t>
         </is>
       </c>
       <c r="G54" s="12" t="inlineStr">
@@ -14937,12 +14937,12 @@
       </c>
       <c r="H54" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I54" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as auditor (Auditor).
+          <t>1. Sign in as Audrey Lim (Auditor).
 2. Open User Access Reports › User Access Audit Log; Audit Trail.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -15006,7 +15006,7 @@
       </c>
       <c r="F55" s="12" t="inlineStr">
         <is>
-          <t>auditor</t>
+          <t>Audrey Lim</t>
         </is>
       </c>
       <c r="G55" s="12" t="inlineStr">
@@ -15016,12 +15016,12 @@
       </c>
       <c r="H55" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I55" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as auditor (Auditor).
+          <t>1. Sign in as Audrey Lim (Auditor).
 2. Open User Access Reports › User Access Audit Log; Audit Trail.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -15085,7 +15085,7 @@
       </c>
       <c r="F56" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G56" s="12" t="inlineStr">
@@ -15095,12 +15095,12 @@
       </c>
       <c r="H56" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I56" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as requestor (Requestor).
+          <t>1. Sign in as Rhea Santiago (Requestor).
 2. Open Login page; any screen.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -15164,7 +15164,7 @@
       </c>
       <c r="F57" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G57" s="12" t="inlineStr">
@@ -15174,12 +15174,12 @@
       </c>
       <c r="H57" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I57" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as requestor (Requestor).
+          <t>1. Sign in as Rhea Santiago (Requestor).
 2. Open Login page; any screen.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -15243,7 +15243,7 @@
       </c>
       <c r="F58" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G58" s="12" t="inlineStr">
@@ -15253,12 +15253,12 @@
       </c>
       <c r="H58" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I58" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as requestor (Requestor).
+          <t>1. Sign in as Rhea Santiago (Requestor).
 2. Open Login page; any screen.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -15322,7 +15322,7 @@
       </c>
       <c r="F59" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G59" s="12" t="inlineStr">
@@ -15332,12 +15332,12 @@
       </c>
       <c r="H59" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I59" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as requestor (Requestor).
+          <t>1. Sign in as Rhea Santiago (Requestor).
 2. Open Login page; any screen.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -15401,7 +15401,7 @@
       </c>
       <c r="F60" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G60" s="12" t="inlineStr">
@@ -15411,12 +15411,12 @@
       </c>
       <c r="H60" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I60" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as requestor (Requestor).
+          <t>1. Sign in as Rhea Santiago (Requestor).
 2. Open Login page; any screen.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -15480,7 +15480,7 @@
       </c>
       <c r="F61" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G61" s="12" t="inlineStr">
@@ -15490,12 +15490,12 @@
       </c>
       <c r="H61" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I61" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as requestor (Requestor).
+          <t>1. Sign in as Rhea Santiago (Requestor).
 2. Open Login page; any screen.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -15559,7 +15559,7 @@
       </c>
       <c r="F62" s="12" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>Samuel Cruz</t>
         </is>
       </c>
       <c r="G62" s="12" t="inlineStr">
@@ -15569,12 +15569,12 @@
       </c>
       <c r="H62" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I62" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as admin (System Administrator).
+          <t>1. Sign in as Samuel Cruz (System Administrator).
 2. Open Administration › Users.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -15638,7 +15638,7 @@
       </c>
       <c r="F63" s="12" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>Samuel Cruz</t>
         </is>
       </c>
       <c r="G63" s="12" t="inlineStr">
@@ -15648,12 +15648,12 @@
       </c>
       <c r="H63" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I63" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as admin (System Administrator).
+          <t>1. Sign in as Samuel Cruz (System Administrator).
 2. Open Administration › Users.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -15717,7 +15717,7 @@
       </c>
       <c r="F64" s="12" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>Samuel Cruz</t>
         </is>
       </c>
       <c r="G64" s="12" t="inlineStr">
@@ -15727,12 +15727,12 @@
       </c>
       <c r="H64" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I64" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as admin (System Administrator).
+          <t>1. Sign in as Samuel Cruz (System Administrator).
 2. Open Administration › Users.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -15796,7 +15796,7 @@
       </c>
       <c r="F65" s="12" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>Samuel Cruz</t>
         </is>
       </c>
       <c r="G65" s="12" t="inlineStr">
@@ -15806,12 +15806,12 @@
       </c>
       <c r="H65" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I65" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as admin (System Administrator).
+          <t>1. Sign in as Samuel Cruz (System Administrator).
 2. Open Administration › Users; Access Requests.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -15875,7 +15875,7 @@
       </c>
       <c r="F66" s="12" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>Samuel Cruz</t>
         </is>
       </c>
       <c r="G66" s="12" t="inlineStr">
@@ -15885,12 +15885,12 @@
       </c>
       <c r="H66" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I66" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as admin (System Administrator).
+          <t>1. Sign in as Samuel Cruz (System Administrator).
 2. Open Administration › Users; Access Requests.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -15954,7 +15954,7 @@
       </c>
       <c r="F67" s="12" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>Samuel Cruz</t>
         </is>
       </c>
       <c r="G67" s="12" t="inlineStr">
@@ -15964,12 +15964,12 @@
       </c>
       <c r="H67" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I67" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as admin (System Administrator).
+          <t>1. Sign in as Samuel Cruz (System Administrator).
 2. Open Administration › Users; Access Requests.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -16037,7 +16037,7 @@
       </c>
       <c r="F68" s="12" t="inlineStr">
         <is>
-          <t>badmin</t>
+          <t>Bea Villanueva</t>
         </is>
       </c>
       <c r="G68" s="12" t="inlineStr">
@@ -16047,12 +16047,12 @@
       </c>
       <c r="H68" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I68" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as badmin (Business Administrator).
+          <t>1. Sign in as Bea Villanueva (Business Administrator).
 2. Open User Access › Group Profile Requests; Roles &amp; Permissions.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -16120,7 +16120,7 @@
       </c>
       <c r="F69" s="12" t="inlineStr">
         <is>
-          <t>badmin</t>
+          <t>Bea Villanueva</t>
         </is>
       </c>
       <c r="G69" s="12" t="inlineStr">
@@ -16130,12 +16130,12 @@
       </c>
       <c r="H69" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I69" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as badmin (Business Administrator).
+          <t>1. Sign in as Bea Villanueva (Business Administrator).
 2. Open User Access › Group Profile Requests; Roles &amp; Permissions.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -16203,7 +16203,7 @@
       </c>
       <c r="F70" s="12" t="inlineStr">
         <is>
-          <t>badmin</t>
+          <t>Bea Villanueva</t>
         </is>
       </c>
       <c r="G70" s="12" t="inlineStr">
@@ -16213,12 +16213,12 @@
       </c>
       <c r="H70" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I70" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as badmin (Business Administrator).
+          <t>1. Sign in as Bea Villanueva (Business Administrator).
 2. Open User Access › Group Profile Requests; Roles &amp; Permissions.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -16286,7 +16286,7 @@
       </c>
       <c r="F71" s="12" t="inlineStr">
         <is>
-          <t>badmin</t>
+          <t>Bea Villanueva</t>
         </is>
       </c>
       <c r="G71" s="12" t="inlineStr">
@@ -16296,12 +16296,12 @@
       </c>
       <c r="H71" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I71" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as badmin (Business Administrator).
+          <t>1. Sign in as Bea Villanueva (Business Administrator).
 2. Open User Access › Group Profile Requests; Roles &amp; Permissions.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -16369,7 +16369,7 @@
       </c>
       <c r="F72" s="12" t="inlineStr">
         <is>
-          <t>badmin</t>
+          <t>Bea Villanueva</t>
         </is>
       </c>
       <c r="G72" s="12" t="inlineStr">
@@ -16379,12 +16379,12 @@
       </c>
       <c r="H72" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I72" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as badmin (Business Administrator).
+          <t>1. Sign in as Bea Villanueva (Business Administrator).
 2. Open User Access › Group Profile Requests; Roles &amp; Permissions.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -16452,7 +16452,7 @@
       </c>
       <c r="F73" s="12" t="inlineStr">
         <is>
-          <t>badmin</t>
+          <t>Bea Villanueva</t>
         </is>
       </c>
       <c r="G73" s="12" t="inlineStr">
@@ -16462,12 +16462,12 @@
       </c>
       <c r="H73" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I73" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as badmin (Business Administrator).
+          <t>1. Sign in as Bea Villanueva (Business Administrator).
 2. Open User Access › Group Profile Requests; Roles &amp; Permissions.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -16535,7 +16535,7 @@
       </c>
       <c r="F74" s="12" t="inlineStr">
         <is>
-          <t>badmin</t>
+          <t>Bea Villanueva</t>
         </is>
       </c>
       <c r="G74" s="12" t="inlineStr">
@@ -16545,12 +16545,12 @@
       </c>
       <c r="H74" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I74" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as badmin (Business Administrator).
+          <t>1. Sign in as Bea Villanueva (Business Administrator).
 2. Open User Access › Group Profile Requests; Roles &amp; Permissions.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -16618,7 +16618,7 @@
       </c>
       <c r="F75" s="12" t="inlineStr">
         <is>
-          <t>badmin</t>
+          <t>Bea Villanueva</t>
         </is>
       </c>
       <c r="G75" s="12" t="inlineStr">
@@ -16628,12 +16628,12 @@
       </c>
       <c r="H75" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I75" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as badmin (Business Administrator).
+          <t>1. Sign in as Bea Villanueva (Business Administrator).
 2. Open User Access › Group Profile Requests; Roles &amp; Permissions.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -16701,7 +16701,7 @@
       </c>
       <c r="F76" s="12" t="inlineStr">
         <is>
-          <t>badmin</t>
+          <t>Bea Villanueva</t>
         </is>
       </c>
       <c r="G76" s="12" t="inlineStr">
@@ -16711,12 +16711,12 @@
       </c>
       <c r="H76" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I76" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as badmin (Business Administrator).
+          <t>1. Sign in as Bea Villanueva (Business Administrator).
 2. Open User Access › Group Profile Requests; Roles &amp; Permissions.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -16784,7 +16784,7 @@
       </c>
       <c r="F77" s="12" t="inlineStr">
         <is>
-          <t>badmin</t>
+          <t>Bea Villanueva</t>
         </is>
       </c>
       <c r="G77" s="12" t="inlineStr">
@@ -16794,12 +16794,12 @@
       </c>
       <c r="H77" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I77" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as badmin (Business Administrator).
+          <t>1. Sign in as Bea Villanueva (Business Administrator).
 2. Open User Access › Group Profile Requests.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -16867,7 +16867,7 @@
       </c>
       <c r="F78" s="12" t="inlineStr">
         <is>
-          <t>badmin</t>
+          <t>Bea Villanueva</t>
         </is>
       </c>
       <c r="G78" s="12" t="inlineStr">
@@ -16877,12 +16877,12 @@
       </c>
       <c r="H78" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I78" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as badmin (Business Administrator).
+          <t>1. Sign in as Bea Villanueva (Business Administrator).
 2. Open User Access › Group Profile Requests.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -16950,7 +16950,7 @@
       </c>
       <c r="F79" s="12" t="inlineStr">
         <is>
-          <t>auditor</t>
+          <t>Audrey Lim</t>
         </is>
       </c>
       <c r="G79" s="12" t="inlineStr">
@@ -16960,12 +16960,12 @@
       </c>
       <c r="H79" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I79" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as auditor (Auditor).
+          <t>1. Sign in as Audrey Lim (Auditor).
 2. Open User Access › User Access Reports.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -16977,7 +16977,7 @@
       </c>
       <c r="K79" s="12" t="inlineStr">
         <is>
-          <t>The Access Requests report lists the requests of a date range with their status and approver.</t>
+          <t>The Access Requests report lists the requests of a date range with their status and Andres Bautista (another approver).</t>
         </is>
       </c>
       <c r="L79" s="12" t="inlineStr">
@@ -17033,7 +17033,7 @@
       </c>
       <c r="F80" s="12" t="inlineStr">
         <is>
-          <t>auditor</t>
+          <t>Audrey Lim</t>
         </is>
       </c>
       <c r="G80" s="12" t="inlineStr">
@@ -17043,12 +17043,12 @@
       </c>
       <c r="H80" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I80" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as auditor (Auditor).
+          <t>1. Sign in as Audrey Lim (Auditor).
 2. Open User Access › User Access Reports.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -17116,7 +17116,7 @@
       </c>
       <c r="F81" s="12" t="inlineStr">
         <is>
-          <t>auditor</t>
+          <t>Audrey Lim</t>
         </is>
       </c>
       <c r="G81" s="12" t="inlineStr">
@@ -17126,12 +17126,12 @@
       </c>
       <c r="H81" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I81" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as auditor (Auditor).
+          <t>1. Sign in as Audrey Lim (Auditor).
 2. Open User Access Reports › User Access Audit Log; Audit Trail.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -17199,7 +17199,7 @@
       </c>
       <c r="F82" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G82" s="12" t="inlineStr">
@@ -17209,12 +17209,12 @@
       </c>
       <c r="H82" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I82" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as requestor (Requestor).
+          <t>1. Sign in as Rhea Santiago (Requestor).
 2. Open User Access › Access Requests › New Request.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -17282,7 +17282,7 @@
       </c>
       <c r="F83" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G83" s="12" t="inlineStr">
@@ -17292,12 +17292,12 @@
       </c>
       <c r="H83" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I83" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as requestor (Requestor).
+          <t>1. Sign in as Rhea Santiago (Requestor).
 2. Open User Access › Access Requests › New Request.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -17365,7 +17365,7 @@
       </c>
       <c r="F84" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G84" s="12" t="inlineStr">
@@ -17375,12 +17375,12 @@
       </c>
       <c r="H84" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I84" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as requestor (Requestor).
+          <t>1. Sign in as Rhea Santiago (Requestor).
 2. Open User Access › Access Requests › New Request.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -17448,7 +17448,7 @@
       </c>
       <c r="F85" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G85" s="12" t="inlineStr">
@@ -17458,12 +17458,12 @@
       </c>
       <c r="H85" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I85" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as requestor (Requestor).
+          <t>1. Sign in as Rhea Santiago (Requestor).
 2. Open User Access › Access Requests › New Request.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -17531,7 +17531,7 @@
       </c>
       <c r="F86" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G86" s="12" t="inlineStr">
@@ -17541,12 +17541,12 @@
       </c>
       <c r="H86" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I86" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as requestor (Requestor).
+          <t>1. Sign in as Rhea Santiago (Requestor).
 2. Open User Access › Access Requests › New Request.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -17558,7 +17558,7 @@
       </c>
       <c r="K86" s="12" t="inlineStr">
         <is>
-          <t>A request for a013000196 with the profile Marketing Account Officer, once approved, creates the user.</t>
+          <t>A request for Isabel Navarro with the profile Marketing Account Officer, once approved, creates the user.</t>
         </is>
       </c>
       <c r="L86" s="12" t="inlineStr">
@@ -17614,7 +17614,7 @@
       </c>
       <c r="F87" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G87" s="12" t="inlineStr">
@@ -17624,12 +17624,12 @@
       </c>
       <c r="H87" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I87" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as requestor (Requestor).
+          <t>1. Sign in as Rhea Santiago (Requestor).
 2. Open User Access › Access Requests › New Request.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -17697,7 +17697,7 @@
       </c>
       <c r="F88" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G88" s="12" t="inlineStr">
@@ -17707,12 +17707,12 @@
       </c>
       <c r="H88" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I88" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as requestor (Requestor).
+          <t>1. Sign in as Rhea Santiago (Requestor).
 2. Open User Access › Access Requests › New Request.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -17780,7 +17780,7 @@
       </c>
       <c r="F89" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G89" s="12" t="inlineStr">
@@ -17790,12 +17790,12 @@
       </c>
       <c r="H89" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I89" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as requestor (Requestor).
+          <t>1. Sign in as Rhea Santiago (Requestor).
 2. Open User Access › Access Requests › New Request.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -17863,7 +17863,7 @@
       </c>
       <c r="F90" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G90" s="12" t="inlineStr">
@@ -17873,12 +17873,12 @@
       </c>
       <c r="H90" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I90" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as requestor (Requestor).
+          <t>1. Sign in as Rhea Santiago (Requestor).
 2. Open User Access › Access Requests › New Request.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -17946,7 +17946,7 @@
       </c>
       <c r="F91" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G91" s="12" t="inlineStr">
@@ -17956,12 +17956,12 @@
       </c>
       <c r="H91" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I91" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as requestor (Requestor).
+          <t>1. Sign in as Rhea Santiago (Requestor).
 2. Open User Access › Access Requests › New Request.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -18029,7 +18029,7 @@
       </c>
       <c r="F92" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G92" s="12" t="inlineStr">
@@ -18039,12 +18039,12 @@
       </c>
       <c r="H92" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I92" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as requestor (Requestor).
+          <t>1. Sign in as Rhea Santiago (Requestor).
 2. Open User Access › Access Requests › New Request.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -18112,7 +18112,7 @@
       </c>
       <c r="F93" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G93" s="12" t="inlineStr">
@@ -18122,12 +18122,12 @@
       </c>
       <c r="H93" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I93" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as requestor (Requestor).
+          <t>1. Sign in as Rhea Santiago (Requestor).
 2. Open User Access › Access Requests › New Request.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -18195,7 +18195,7 @@
       </c>
       <c r="F94" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G94" s="12" t="inlineStr">
@@ -18205,12 +18205,12 @@
       </c>
       <c r="H94" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I94" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as requestor (Requestor).
+          <t>1. Sign in as Rhea Santiago (Requestor).
 2. Open User Access › Access Requests › New Request.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="F95" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G95" s="12" t="inlineStr">
@@ -18288,12 +18288,12 @@
       </c>
       <c r="H95" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I95" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as requestor (Requestor).
+          <t>1. Sign in as Rhea Santiago (Requestor).
 2. Open User Access › Access Requests › New Request.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -18361,7 +18361,7 @@
       </c>
       <c r="F96" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G96" s="12" t="inlineStr">
@@ -18371,12 +18371,12 @@
       </c>
       <c r="H96" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I96" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as requestor (Requestor).
+          <t>1. Sign in as Rhea Santiago (Requestor).
 2. Open User Access › Access Requests › New Request.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -18444,7 +18444,7 @@
       </c>
       <c r="F97" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G97" s="12" t="inlineStr">
@@ -18454,12 +18454,12 @@
       </c>
       <c r="H97" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I97" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as requestor (Requestor).
+          <t>1. Sign in as Rhea Santiago (Requestor).
 2. Open User Access › Access Requests › New Request.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -18527,7 +18527,7 @@
       </c>
       <c r="F98" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G98" s="12" t="inlineStr">
@@ -18537,12 +18537,12 @@
       </c>
       <c r="H98" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I98" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as requestor (Requestor).
+          <t>1. Sign in as Rhea Santiago (Requestor).
 2. Open User Access › Access Requests › New Request.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -18610,7 +18610,7 @@
       </c>
       <c r="F99" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G99" s="12" t="inlineStr">
@@ -18620,12 +18620,12 @@
       </c>
       <c r="H99" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I99" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as requestor (Requestor).
+          <t>1. Sign in as Rhea Santiago (Requestor).
 2. Open User Access › Access Requests › New Request.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -18689,7 +18689,7 @@
       </c>
       <c r="F100" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G100" s="12" t="inlineStr">
@@ -18699,12 +18699,12 @@
       </c>
       <c r="H100" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I100" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as requestor (Requestor).
+          <t>1. Sign in as Rhea Santiago (Requestor).
 2. Open User Access › Access Requests › New Request.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -18768,7 +18768,7 @@
       </c>
       <c r="F101" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G101" s="12" t="inlineStr">
@@ -18778,12 +18778,12 @@
       </c>
       <c r="H101" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I101" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as requestor (Requestor).
+          <t>1. Sign in as Rhea Santiago (Requestor).
 2. Open User Access › Access Requests › New Request.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -18851,7 +18851,7 @@
       </c>
       <c r="F102" s="12" t="inlineStr">
         <is>
-          <t>uamapprover</t>
+          <t>Ulysses Abad</t>
         </is>
       </c>
       <c r="G102" s="12" t="inlineStr">
@@ -18861,12 +18861,12 @@
       </c>
       <c r="H102" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I102" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as uamapprover (Approver).
+          <t>1. Sign in as Ulysses Abad (Approver).
 2. Open User Access › Access Requests (Assigned to Me).
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="F103" s="12" t="inlineStr">
         <is>
-          <t>uamapprover</t>
+          <t>Ulysses Abad</t>
         </is>
       </c>
       <c r="G103" s="12" t="inlineStr">
@@ -18944,12 +18944,12 @@
       </c>
       <c r="H103" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I103" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as uamapprover (Approver).
+          <t>1. Sign in as Ulysses Abad (Approver).
 2. Open User Access › Access Requests (Assigned to Me).
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -19017,7 +19017,7 @@
       </c>
       <c r="F104" s="12" t="inlineStr">
         <is>
-          <t>uamapprover</t>
+          <t>Ulysses Abad</t>
         </is>
       </c>
       <c r="G104" s="12" t="inlineStr">
@@ -19027,12 +19027,12 @@
       </c>
       <c r="H104" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I104" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as uamapprover (Approver).
+          <t>1. Sign in as Ulysses Abad (Approver).
 2. Open User Access › Access Requests (Assigned to Me).
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -19100,7 +19100,7 @@
       </c>
       <c r="F105" s="12" t="inlineStr">
         <is>
-          <t>uamapprover</t>
+          <t>Ulysses Abad</t>
         </is>
       </c>
       <c r="G105" s="12" t="inlineStr">
@@ -19110,12 +19110,12 @@
       </c>
       <c r="H105" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I105" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as uamapprover (Approver).
+          <t>1. Sign in as Ulysses Abad (Approver).
 2. Open User Access › Access Requests (Assigned to Me).
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -19183,7 +19183,7 @@
       </c>
       <c r="F106" s="12" t="inlineStr">
         <is>
-          <t>uamapprover</t>
+          <t>Ulysses Abad</t>
         </is>
       </c>
       <c r="G106" s="12" t="inlineStr">
@@ -19193,12 +19193,12 @@
       </c>
       <c r="H106" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I106" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as uamapprover (Approver).
+          <t>1. Sign in as Ulysses Abad (Approver).
 2. Open User Access › Access Requests (Assigned to Me).
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -19266,7 +19266,7 @@
       </c>
       <c r="F107" s="12" t="inlineStr">
         <is>
-          <t>uamapprover</t>
+          <t>Ulysses Abad</t>
         </is>
       </c>
       <c r="G107" s="12" t="inlineStr">
@@ -19276,12 +19276,12 @@
       </c>
       <c r="H107" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I107" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as uamapprover (Approver).
+          <t>1. Sign in as Ulysses Abad (Approver).
 2. Open User Access › Access Requests (Assigned to Me).
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -19349,7 +19349,7 @@
       </c>
       <c r="F108" s="12" t="inlineStr">
         <is>
-          <t>uamapprover</t>
+          <t>Ulysses Abad</t>
         </is>
       </c>
       <c r="G108" s="12" t="inlineStr">
@@ -19359,12 +19359,12 @@
       </c>
       <c r="H108" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I108" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as uamapprover (Approver).
+          <t>1. Sign in as Ulysses Abad (Approver).
 2. Open User Access › Access Requests (Assigned to Me).
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -19432,7 +19432,7 @@
       </c>
       <c r="F109" s="12" t="inlineStr">
         <is>
-          <t>uamapprover</t>
+          <t>Ulysses Abad</t>
         </is>
       </c>
       <c r="G109" s="12" t="inlineStr">
@@ -19442,12 +19442,12 @@
       </c>
       <c r="H109" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I109" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as uamapprover (Approver).
+          <t>1. Sign in as Ulysses Abad (Approver).
 2. Open User Access › Access Requests (Assigned to Me).
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -19515,7 +19515,7 @@
       </c>
       <c r="F110" s="12" t="inlineStr">
         <is>
-          <t>uamapprover</t>
+          <t>Ulysses Abad</t>
         </is>
       </c>
       <c r="G110" s="12" t="inlineStr">
@@ -19525,12 +19525,12 @@
       </c>
       <c r="H110" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I110" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as uamapprover (Approver).
+          <t>1. Sign in as Ulysses Abad (Approver).
 2. Open User Access › Access Requests (Assigned to Me).
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -19598,7 +19598,7 @@
       </c>
       <c r="F111" s="12" t="inlineStr">
         <is>
-          <t>uamapprover</t>
+          <t>Ulysses Abad</t>
         </is>
       </c>
       <c r="G111" s="12" t="inlineStr">
@@ -19608,12 +19608,12 @@
       </c>
       <c r="H111" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I111" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as uamapprover (Approver).
+          <t>1. Sign in as Ulysses Abad (Approver).
 2. Open User Access › Access Requests (Assigned to Me).
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -19681,7 +19681,7 @@
       </c>
       <c r="F112" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G112" s="12" t="inlineStr">
@@ -19691,12 +19691,12 @@
       </c>
       <c r="H112" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I112" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as requestor (Requestor).
+          <t>1. Sign in as Rhea Santiago (Requestor).
 2. Open User Access › Bulk Request.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -19764,7 +19764,7 @@
       </c>
       <c r="F113" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G113" s="12" t="inlineStr">
@@ -19774,12 +19774,12 @@
       </c>
       <c r="H113" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I113" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as requestor (Requestor).
+          <t>1. Sign in as Rhea Santiago (Requestor).
 2. Open User Access › Bulk Request.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -19847,7 +19847,7 @@
       </c>
       <c r="F114" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G114" s="12" t="inlineStr">
@@ -19857,12 +19857,12 @@
       </c>
       <c r="H114" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I114" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as requestor (Requestor).
+          <t>1. Sign in as Rhea Santiago (Requestor).
 2. Open User Access › Bulk Request.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -19926,7 +19926,7 @@
       </c>
       <c r="F115" s="12" t="inlineStr">
         <is>
-          <t>infosec</t>
+          <t>Information Security Officer</t>
         </is>
       </c>
       <c r="G115" s="12" t="inlineStr">
@@ -19936,12 +19936,12 @@
       </c>
       <c r="H115" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I115" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as infosec (Information Security Officer).
+          <t>1. Sign in as the Information Security Officer.
 2. Open User Access › Separation of Duties; System Parameters.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -20005,7 +20005,7 @@
       </c>
       <c r="F116" s="12" t="inlineStr">
         <is>
-          <t>infosec</t>
+          <t>Information Security Officer</t>
         </is>
       </c>
       <c r="G116" s="12" t="inlineStr">
@@ -20015,12 +20015,12 @@
       </c>
       <c r="H116" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I116" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as infosec (Information Security Officer).
+          <t>1. Sign in as the Information Security Officer.
 2. Open User Access › Separation of Duties; System Parameters.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -20084,7 +20084,7 @@
       </c>
       <c r="F117" s="12" t="inlineStr">
         <is>
-          <t>infosec</t>
+          <t>Information Security Officer</t>
         </is>
       </c>
       <c r="G117" s="12" t="inlineStr">
@@ -20094,12 +20094,12 @@
       </c>
       <c r="H117" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I117" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as infosec (Information Security Officer).
+          <t>1. Sign in as the Information Security Officer.
 2. Open User Access › Separation of Duties; System Parameters.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -20163,7 +20163,7 @@
       </c>
       <c r="F118" s="12" t="inlineStr">
         <is>
-          <t>infosec</t>
+          <t>Information Security Officer</t>
         </is>
       </c>
       <c r="G118" s="12" t="inlineStr">
@@ -20173,12 +20173,12 @@
       </c>
       <c r="H118" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I118" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as infosec (Information Security Officer).
+          <t>1. Sign in as the Information Security Officer.
 2. Open User Access › Separation of Duties; System Parameters.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -20246,7 +20246,7 @@
       </c>
       <c r="F119" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G119" s="12" t="inlineStr">
@@ -20256,12 +20256,12 @@
       </c>
       <c r="H119" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I119" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as requestor (Requestor).
+          <t>1. Sign in as Rhea Santiago (Requestor).
 2. Open Notifications (bell); test mailbox.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -20329,7 +20329,7 @@
       </c>
       <c r="F120" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G120" s="12" t="inlineStr">
@@ -20339,12 +20339,12 @@
       </c>
       <c r="H120" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I120" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as requestor (Requestor).
+          <t>1. Sign in as Rhea Santiago (Requestor).
 2. Open Notifications (bell); test mailbox.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -20408,7 +20408,7 @@
       </c>
       <c r="F121" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G121" s="12" t="inlineStr">
@@ -20418,12 +20418,12 @@
       </c>
       <c r="H121" s="12" t="inlineStr">
         <is>
-          <t>Users, profiles and requests of the SIT/UAT data (TD-UA-01 to TD-UA-03).</t>
+          <t>Users, profiles and requests of the test data prepared for the walkthrough (TD-UA-01 to TD-UA-03).</t>
         </is>
       </c>
       <c r="I121" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as requestor (Requestor).
+          <t>1. Sign in as Rhea Santiago (Requestor).
 2. Open Notifications (bell); test mailbox.
 3. Bring about the situation of the acceptance criterion and observe the result.</t>
         </is>
@@ -20491,7 +20491,7 @@
       </c>
       <c r="F122" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G122" s="12" t="inlineStr">
@@ -20506,7 +20506,7 @@
       </c>
       <c r="I122" s="12" t="inlineStr">
         <is>
-          <t>1. Log in as requestor; open the side menu.</t>
+          <t>1. Log in as Rhea Santiago (Requestor); open the side menu.</t>
         </is>
       </c>
       <c r="J122" s="12" t="inlineStr">
@@ -20572,7 +20572,7 @@
       </c>
       <c r="F123" s="12" t="inlineStr">
         <is>
-          <t>badmin</t>
+          <t>Bea Villanueva</t>
         </is>
       </c>
       <c r="G123" s="12" t="inlineStr">
@@ -20582,12 +20582,12 @@
       </c>
       <c r="H123" s="12" t="inlineStr">
         <is>
-          <t>badmin also holds Requestor (granted through a request).</t>
+          <t>Bea Villanueva (Business Administrator) also holds Requestor (granted through a request).</t>
         </is>
       </c>
       <c r="I123" s="12" t="inlineStr">
         <is>
-          <t>1. Log in as badmin; open the side menu.</t>
+          <t>1. Log in as Bea Villanueva (Business Administrator); open the side menu.</t>
         </is>
       </c>
       <c r="J123" s="12" t="inlineStr">
@@ -20653,7 +20653,7 @@
       </c>
       <c r="F124" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G124" s="12" t="inlineStr">
@@ -20668,7 +20668,7 @@
       </c>
       <c r="I124" s="12" t="inlineStr">
         <is>
-          <t>1. Enter requestor and a wrong password.</t>
+          <t>1. Enter Rhea Santiago (Requestor) and a wrong password.</t>
         </is>
       </c>
       <c r="J124" s="12" t="inlineStr">
@@ -20734,7 +20734,7 @@
       </c>
       <c r="F125" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G125" s="12" t="inlineStr">
@@ -20749,7 +20749,7 @@
       </c>
       <c r="I125" s="12" t="inlineStr">
         <is>
-          <t>1. Enter requestor2 with a wrong password three times; then the correct password.</t>
+          <t>1. Enter a second Requestor with a wrong password three times; then the correct password.</t>
         </is>
       </c>
       <c r="J125" s="12" t="inlineStr">
@@ -20815,7 +20815,7 @@
       </c>
       <c r="F126" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G126" s="12" t="inlineStr">
@@ -20896,7 +20896,7 @@
       </c>
       <c r="F127" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G127" s="12" t="inlineStr">
@@ -20911,7 +20911,7 @@
       </c>
       <c r="I127" s="12" t="inlineStr">
         <is>
-          <t>1. Enter uamapprover2 with a wrong password twice; then the correct password.</t>
+          <t>1. Enter a second Approver with a wrong password twice; then the correct password.</t>
         </is>
       </c>
       <c r="J127" s="12" t="inlineStr">
@@ -20977,7 +20977,7 @@
       </c>
       <c r="F128" s="12" t="inlineStr">
         <is>
-          <t>auditor</t>
+          <t>Audrey Lim</t>
         </is>
       </c>
       <c r="G128" s="12" t="inlineStr">
@@ -20992,7 +20992,7 @@
       </c>
       <c r="I128" s="12" t="inlineStr">
         <is>
-          <t>1. Open Administration &gt; Audit Trail for today and requestor2.</t>
+          <t>1. Open Administration &gt; Audit Trail for today and a second Requestor.</t>
         </is>
       </c>
       <c r="J128" s="12" t="inlineStr">
@@ -21058,7 +21058,7 @@
       </c>
       <c r="F129" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Maria Santos</t>
         </is>
       </c>
       <c r="G129" s="12" t="inlineStr">
@@ -21073,7 +21073,7 @@
       </c>
       <c r="I129" s="12" t="inlineStr">
         <is>
-          <t>1. Log in as ao; leave the screen idle for 15 minutes.
+          <t>1. Log in as Maria Santos (business user); leave the screen idle for 15 minutes.
 2. Click Stay Logged In in the warning.</t>
         </is>
       </c>
@@ -21140,7 +21140,7 @@
       </c>
       <c r="F130" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Maria Santos</t>
         </is>
       </c>
       <c r="G130" s="12" t="inlineStr">
@@ -21221,7 +21221,7 @@
       </c>
       <c r="F131" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Maria Santos</t>
         </is>
       </c>
       <c r="G131" s="12" t="inlineStr">
@@ -21302,7 +21302,7 @@
       </c>
       <c r="F132" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Maria Santos</t>
         </is>
       </c>
       <c r="G132" s="12" t="inlineStr">
@@ -21383,7 +21383,7 @@
       </c>
       <c r="F133" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Maria Santos</t>
         </is>
       </c>
       <c r="G133" s="12" t="inlineStr">
@@ -21464,7 +21464,7 @@
       </c>
       <c r="F134" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Maria Santos</t>
         </is>
       </c>
       <c r="G134" s="12" t="inlineStr">
@@ -21479,7 +21479,7 @@
       </c>
       <c r="I134" s="12" t="inlineStr">
         <is>
-          <t>1. Log in as ao; leave the screen idle for 15 minutes.
+          <t>1. Log in as Maria Santos (business user); leave the screen idle for 15 minutes.
 2. Read the warning; click Log Out.</t>
         </is>
       </c>
@@ -21546,7 +21546,7 @@
       </c>
       <c r="F135" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Maria Santos</t>
         </is>
       </c>
       <c r="G135" s="12" t="inlineStr">
@@ -21561,7 +21561,7 @@
       </c>
       <c r="I135" s="12" t="inlineStr">
         <is>
-          <t>1. Log in as ao; stay idle for 30 minutes.
+          <t>1. Log in as Maria Santos (business user); stay idle for 30 minutes.
 2. On the page Session Timed Out click Log In.</t>
         </is>
       </c>
@@ -21572,7 +21572,7 @@
       </c>
       <c r="K135" s="12" t="inlineStr">
         <is>
-          <t>The Login page opens; the audit trail shows the time-out of ao.</t>
+          <t>The Login page opens; the audit trail shows the time-out of Maria Santos (business user).</t>
         </is>
       </c>
       <c r="L135" s="12" t="inlineStr">
@@ -21628,7 +21628,7 @@
       </c>
       <c r="F136" s="12" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>Samuel Cruz</t>
         </is>
       </c>
       <c r="G136" s="12" t="inlineStr">
@@ -21643,7 +21643,7 @@
       </c>
       <c r="I136" s="12" t="inlineStr">
         <is>
-          <t>1. Log in as ao; stay idle for 15 minutes, then for 30 minutes.</t>
+          <t>1. Log in as Maria Santos (business user); stay idle for 15 minutes, then for 30 minutes.</t>
         </is>
       </c>
       <c r="J136" s="12" t="inlineStr">
@@ -21709,7 +21709,7 @@
       </c>
       <c r="F137" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G137" s="12" t="inlineStr">
@@ -21725,8 +21725,8 @@
       <c r="I137" s="12" t="inlineStr">
         <is>
           <t>1. Open the system and click Sign in with the BDO identity provider.
-2. Sign in at EIAM with the test account of requestor.
-3. As the infrastructure administrator check the stored sign-in data of requestor.</t>
+2. Sign in at EIAM with the test account of Rhea Santiago (Requestor).
+3. As the infrastructure administrator check the stored sign-in data of Rhea Santiago (Requestor).</t>
         </is>
       </c>
       <c r="J137" s="12" t="inlineStr">
@@ -21736,7 +21736,7 @@
       </c>
       <c r="K137" s="12" t="inlineStr">
         <is>
-          <t>The home page opens with the Requestor menu; the audit shows the sign-in with the method OIDC; no password is kept for requestor.</t>
+          <t>The home page opens with the Requestor menu; the audit shows the sign-in with the method OIDC; no password is kept for Rhea Santiago (Requestor).</t>
         </is>
       </c>
       <c r="L137" s="12" t="inlineStr">
@@ -21792,7 +21792,7 @@
       </c>
       <c r="F138" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G138" s="12" t="inlineStr">
@@ -21873,7 +21873,7 @@
       </c>
       <c r="F139" s="12" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>Samuel Cruz</t>
         </is>
       </c>
       <c r="G139" s="12" t="inlineStr">
@@ -21888,7 +21888,7 @@
       </c>
       <c r="I139" s="12" t="inlineStr">
         <is>
-          <t>1. On the Login page sign in as admin with the local password and the second factor.</t>
+          <t>1. On the Login page sign in as Samuel Cruz (System Administrator) with the local password and the second factor.</t>
         </is>
       </c>
       <c r="J139" s="12" t="inlineStr">
@@ -21954,7 +21954,7 @@
       </c>
       <c r="F140" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G140" s="12" t="inlineStr">
@@ -21969,7 +21969,7 @@
       </c>
       <c r="I140" s="12" t="inlineStr">
         <is>
-          <t>1. On the Login page try to sign in as requestor with a password.</t>
+          <t>1. On the Login page try to sign in as Rhea Santiago (Requestor) with a password.</t>
         </is>
       </c>
       <c r="J140" s="12" t="inlineStr">
@@ -21979,7 +21979,7 @@
       </c>
       <c r="K140" s="12" t="inlineStr">
         <is>
-          <t>The sign-in is refused; only Sign in with the BDO identity provider opens a session for requestor.</t>
+          <t>The sign-in is refused; only Sign in with the BDO identity provider opens a session for Rhea Santiago (Requestor).</t>
         </is>
       </c>
       <c r="L140" s="12" t="inlineStr">
@@ -22035,7 +22035,7 @@
       </c>
       <c r="F141" s="12" t="inlineStr">
         <is>
-          <t>badmin</t>
+          <t>Bea Villanueva</t>
         </is>
       </c>
       <c r="G141" s="12" t="inlineStr">
@@ -22050,7 +22050,7 @@
       </c>
       <c r="I141" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in at EIAM with the test account of badmin.</t>
+          <t>1. Sign in at EIAM with the test account of Bea Villanueva (Business Administrator).</t>
         </is>
       </c>
       <c r="J141" s="12" t="inlineStr">
@@ -22060,7 +22060,7 @@
       </c>
       <c r="K141" s="12" t="inlineStr">
         <is>
-          <t>The menu is that of the system roles of badmin.</t>
+          <t>The menu is that of the system roles of Bea Villanueva (Business Administrator).</t>
         </is>
       </c>
       <c r="L141" s="12" t="inlineStr">
@@ -22116,7 +22116,7 @@
       </c>
       <c r="F142" s="12" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>Samuel Cruz</t>
         </is>
       </c>
       <c r="G142" s="12" t="inlineStr">
@@ -22131,7 +22131,7 @@
       </c>
       <c r="I142" s="12" t="inlineStr">
         <is>
-          <t>1. With the Enterprise SSO test accounts provided under the Integration scope, set up the account BDO\uat.joiner with user ID a013000195 and send joiner.
+          <t>1. With the Enterprise SSO test accounts provided under the Integration scope, set up the account the joiner's directory account with a test user and send joiner.
 2. Change the account to the AD status Disabled and send status change.</t>
         </is>
       </c>
@@ -22142,7 +22142,7 @@
       </c>
       <c r="K142" s="12" t="inlineStr">
         <is>
-          <t>The joiner creates user a013000195 with its directory details (event Applied); the status change deactivates the user and ends the open sessions; both events are listed under Events.</t>
+          <t>The joiner creates a test user with its directory details (event Applied); the status change deactivates the user and ends the open sessions; both events are listed under Events.</t>
         </is>
       </c>
       <c r="L142" s="12" t="inlineStr">
@@ -22198,7 +22198,7 @@
       </c>
       <c r="F143" s="12" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>Samuel Cruz</t>
         </is>
       </c>
       <c r="G143" s="12" t="inlineStr">
@@ -22280,7 +22280,7 @@
       </c>
       <c r="F144" s="12" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>Samuel Cruz</t>
         </is>
       </c>
       <c r="G144" s="12" t="inlineStr">
@@ -22305,7 +22305,7 @@
       </c>
       <c r="K144" s="12" t="inlineStr">
         <is>
-          <t>The account details are shown; user a013000301 is created without group profiles and a joiner event is listed.</t>
+          <t>The account details are shown; a test user is created without group profiles and a joiner event is listed.</t>
         </is>
       </c>
       <c r="L144" s="12" t="inlineStr">
@@ -22361,7 +22361,7 @@
       </c>
       <c r="F145" s="12" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>Samuel Cruz</t>
         </is>
       </c>
       <c r="G145" s="12" t="inlineStr">
@@ -22376,7 +22376,7 @@
       </c>
       <c r="I145" s="12" t="inlineStr">
         <is>
-          <t>1. On Users open the row menu of a013000103 and choose Directory details; click Synchronise Now.</t>
+          <t>1. On Users open the row menu of a test user and choose Directory details; click Synchronise Now.</t>
         </is>
       </c>
       <c r="J145" s="12" t="inlineStr">
@@ -22442,7 +22442,7 @@
       </c>
       <c r="F146" s="12" t="inlineStr">
         <is>
-          <t>auditor</t>
+          <t>Audrey Lim</t>
         </is>
       </c>
       <c r="G146" s="12" t="inlineStr">
@@ -22457,8 +22457,8 @@
       </c>
       <c r="I146" s="12" t="inlineStr">
         <is>
-          <t>1. As requestor click Log Out.
-2. As auditor run the User Access Audit Log for today with log-ins and log-outs included.</t>
+          <t>1. As Rhea Santiago (Requestor) click Log Out.
+2. As Audrey Lim (Auditor) run the User Access Audit Log for today with log-ins and log-outs included.</t>
         </is>
       </c>
       <c r="J146" s="12" t="inlineStr">
@@ -22468,7 +22468,7 @@
       </c>
       <c r="K146" s="12" t="inlineStr">
         <is>
-          <t>The report shows the log-out of requestor with the time.</t>
+          <t>The report shows the log-out of Rhea Santiago (Requestor) with the time.</t>
         </is>
       </c>
       <c r="L146" s="12" t="inlineStr">
@@ -22524,7 +22524,7 @@
       </c>
       <c r="F147" s="12" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>Samuel Cruz</t>
         </is>
       </c>
       <c r="G147" s="12" t="inlineStr">
@@ -22539,7 +22539,7 @@
       </c>
       <c r="I147" s="12" t="inlineStr">
         <is>
-          <t>1. Log in as requestor in one browser; as admin open Administration &gt; Users.</t>
+          <t>1. Log in as Rhea Santiago (Requestor) in one browser; as Samuel Cruz (System Administrator) open Administration &gt; Users.</t>
         </is>
       </c>
       <c r="J147" s="12" t="inlineStr">
@@ -22549,7 +22549,7 @@
       </c>
       <c r="K147" s="12" t="inlineStr">
         <is>
-          <t>requestor shows the status Online.</t>
+          <t>Rhea Santiago (Requestor) shows the status Online.</t>
         </is>
       </c>
       <c r="L147" s="12" t="inlineStr">
@@ -22605,7 +22605,7 @@
       </c>
       <c r="F148" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G148" s="12" t="inlineStr">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="I148" s="12" t="inlineStr">
         <is>
-          <t>1. Keep the sign-in of requestor; log out; repeat an action of the old session outside the screens.</t>
+          <t>1. Keep the sign-in of Rhea Santiago (Requestor); log out; repeat an action of the old session outside the screens.</t>
         </is>
       </c>
       <c r="J148" s="12" t="inlineStr">
@@ -22686,7 +22686,7 @@
       </c>
       <c r="F149" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G149" s="12" t="inlineStr">
@@ -22696,7 +22696,7 @@
       </c>
       <c r="H149" s="12" t="inlineStr">
         <is>
-          <t>the sign-in mode = OIDC on the test environment; requestor signed in through EIAM.</t>
+          <t>the sign-in mode = OIDC on the test environment; Rhea Santiago (Requestor) signed in through EIAM.</t>
         </is>
       </c>
       <c r="I149" s="12" t="inlineStr">
@@ -22768,7 +22768,7 @@
       </c>
       <c r="F150" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G150" s="12" t="inlineStr">
@@ -22849,7 +22849,7 @@
       </c>
       <c r="F151" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G151" s="12" t="inlineStr">
@@ -22930,7 +22930,7 @@
       </c>
       <c r="F152" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G152" s="12" t="inlineStr">
@@ -23011,7 +23011,7 @@
       </c>
       <c r="F153" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G153" s="12" t="inlineStr">
@@ -23092,7 +23092,7 @@
       </c>
       <c r="F154" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G154" s="12" t="inlineStr">
@@ -23173,7 +23173,7 @@
       </c>
       <c r="F155" s="12" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>Samuel Cruz</t>
         </is>
       </c>
       <c r="G155" s="12" t="inlineStr">
@@ -23188,8 +23188,8 @@
       </c>
       <c r="I155" s="12" t="inlineStr">
         <is>
-          <t>1. As admin reset the password of requestor2; note the temporary password.
-2. Log in as requestor2 with it.</t>
+          <t>1. As Samuel Cruz (System Administrator) reset the password of a second Requestor; note the temporary password.
+2. Log in as a second Requestor with it.</t>
         </is>
       </c>
       <c r="J155" s="12" t="inlineStr">
@@ -23255,7 +23255,7 @@
       </c>
       <c r="F156" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G156" s="12" t="inlineStr">
@@ -23265,12 +23265,12 @@
       </c>
       <c r="H156" s="12" t="inlineStr">
         <is>
-          <t>The password date of requestor is set 90 days back in the test environment.</t>
+          <t>The password date of Rhea Santiago (Requestor) is set 90 days back in the test environment.</t>
         </is>
       </c>
       <c r="I156" s="12" t="inlineStr">
         <is>
-          <t>1. Log in as requestor.</t>
+          <t>1. Log in as Rhea Santiago (Requestor).</t>
         </is>
       </c>
       <c r="J156" s="12" t="inlineStr">
@@ -23336,7 +23336,7 @@
       </c>
       <c r="F157" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G157" s="12" t="inlineStr">
@@ -23351,7 +23351,7 @@
       </c>
       <c r="I157" s="12" t="inlineStr">
         <is>
-          <t>1. Click Forgot password?; enter requestor; open the e-mail; set a new password with the link.
+          <t>1. Click Forgot password?; enter Rhea Santiago (Requestor); open the e-mail; set a new password with the link.
 2. Open the same link again.</t>
         </is>
       </c>
@@ -23418,7 +23418,7 @@
       </c>
       <c r="F158" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G158" s="12" t="inlineStr">
@@ -23499,7 +23499,7 @@
       </c>
       <c r="F159" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G159" s="12" t="inlineStr">
@@ -23509,7 +23509,7 @@
       </c>
       <c r="H159" s="12" t="inlineStr">
         <is>
-          <t>The password date of requestor is set 84 days back.</t>
+          <t>The password date of Rhea Santiago (Requestor) is set 84 days back.</t>
         </is>
       </c>
       <c r="I159" s="12" t="inlineStr">
@@ -23524,7 +23524,7 @@
       </c>
       <c r="K159" s="12" t="inlineStr">
         <is>
-          <t>requestor is notified that the password expires within 7 days.</t>
+          <t>Rhea Santiago (Requestor) is notified that the password expires within 7 days.</t>
         </is>
       </c>
       <c r="L159" s="12" t="inlineStr">
@@ -23590,13 +23590,13 @@
       </c>
       <c r="H160" s="12" t="inlineStr">
         <is>
-          <t>The test lead sets the last sign-in of subject user a013000104 to 91 days ago (administration tools of the test environment).</t>
+          <t>The test lead sets the last sign-in of subject a test user to 91 days ago (administration tools of the test environment).</t>
         </is>
       </c>
       <c r="I160" s="12" t="inlineStr">
         <is>
-          <t>1. As admin run the dormant-user run from Scheduled Jobs.
-2. As requestor open Access Requests; as a013000104 try to sign in.</t>
+          <t>1. As Samuel Cruz (System Administrator) run the dormant-user run from Scheduled Jobs.
+2. As Rhea Santiago (Requestor) open Access Requests; as a test user try to sign in.</t>
         </is>
       </c>
       <c r="J160" s="12" t="inlineStr">
@@ -23672,12 +23672,12 @@
       </c>
       <c r="H161" s="12" t="inlineStr">
         <is>
-          <t>The last sign-in of a013000103 is set to 83 days ago.</t>
+          <t>The last sign-in of a test user is set to 83 days ago.</t>
         </is>
       </c>
       <c r="I161" s="12" t="inlineStr">
         <is>
-          <t>1. Run the job; open the notifications and the mailbox of a013000103.</t>
+          <t>1. Run the job; open the notifications and the mailbox of a test user.</t>
         </is>
       </c>
       <c r="J161" s="12" t="inlineStr">
@@ -23824,7 +23824,7 @@
       </c>
       <c r="F163" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G163" s="12" t="inlineStr">
@@ -23839,7 +23839,7 @@
       </c>
       <c r="I163" s="12" t="inlineStr">
         <is>
-          <t>1. New Request, type Enrol new user; enter the data of TD-UA-04; approver uamapprover; remarks; Save Draft.
+          <t>1. New Request, type Enrol new user; enter the data of TD-UA-04; approver Ulysses Abad (Approver); remarks; Save Draft.
 2. The next day open the draft; change the home branch; Submit.</t>
         </is>
       </c>
@@ -23906,7 +23906,7 @@
       </c>
       <c r="F164" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G164" s="12" t="inlineStr">
@@ -23931,7 +23931,7 @@
       </c>
       <c r="K164" s="12" t="inlineStr">
         <is>
-          <t>The draft stays DRAFT and the message is shown. Message: User approver already exists</t>
+          <t>The draft stays DRAFT and the message is shown. Message: User &lt;user ID&gt; already exists</t>
         </is>
       </c>
       <c r="L164" s="12" t="inlineStr">
@@ -23987,7 +23987,7 @@
       </c>
       <c r="F165" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G165" s="12" t="inlineStr">
@@ -24002,7 +24002,7 @@
       </c>
       <c r="I165" s="12" t="inlineStr">
         <is>
-          <t>1. As requestor2 open the address of requestor's draft; send a direct request to edit it.</t>
+          <t>1. As a second Requestor open the address of Rhea Santiago (Requestor)'s draft; send a direct request to edit it.</t>
         </is>
       </c>
       <c r="J165" s="12" t="inlineStr">
@@ -24012,7 +24012,7 @@
       </c>
       <c r="K165" s="12" t="inlineStr">
         <is>
-          <t>The draft is not listed for requestor2; the edit is refused. Message: Only the creator can edit request AR-2026-900001; ACCESS_NOT_REQUESTER</t>
+          <t>The draft is not listed for a second Requestor; the edit is refused. Message: Only the creator can edit request AR-2026-900001; ACCESS_NOT_REQUESTER</t>
         </is>
       </c>
       <c r="L165" s="12" t="inlineStr">
@@ -24068,7 +24068,7 @@
       </c>
       <c r="F166" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G166" s="12" t="inlineStr">
@@ -24149,7 +24149,7 @@
       </c>
       <c r="F167" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G167" s="12" t="inlineStr">
@@ -24230,7 +24230,7 @@
       </c>
       <c r="F168" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G168" s="12" t="inlineStr">
@@ -24311,7 +24311,7 @@
       </c>
       <c r="F169" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G169" s="12" t="inlineStr">
@@ -24392,7 +24392,7 @@
       </c>
       <c r="F170" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G170" s="12" t="inlineStr">
@@ -24417,7 +24417,7 @@
       </c>
       <c r="K170" s="12" t="inlineStr">
         <is>
-          <t>Refused. Message: A request for user a013000101 is already waiting for approval; ACCESS_REQUEST_PENDING</t>
+          <t>Refused. Message: A request for user Maria Santos is already waiting for approval; ACCESS_REQUEST_PENDING</t>
         </is>
       </c>
       <c r="L170" s="12" t="inlineStr">
@@ -24453,7 +24453,7 @@
       </c>
       <c r="B171" s="12" t="inlineStr">
         <is>
-          <t>Enrol a013000196</t>
+          <t>Enrol Isabel Navarro</t>
         </is>
       </c>
       <c r="C171" s="12" t="inlineStr">
@@ -24473,7 +24473,7 @@
       </c>
       <c r="F171" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G171" s="12" t="inlineStr">
@@ -24488,8 +24488,8 @@
       </c>
       <c r="I171" s="12" t="inlineStr">
         <is>
-          <t>1. Enrol new user a013000196, UAT User One, profile Marketing Account Officer; approver uamapprover; submit.
-2. As uamapprover approve; note the temporary password; log in as a013000196.</t>
+          <t>1. Enrol new user Isabel Navarro, Isabel Navarro, profile Marketing Account Officer; approver Ulysses Abad (Approver); submit.
+2. As Ulysses Abad (Approver) approve; note the temporary password; log in as Isabel Navarro.</t>
         </is>
       </c>
       <c r="J171" s="12" t="inlineStr">
@@ -24555,7 +24555,7 @@
       </c>
       <c r="F172" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G172" s="12" t="inlineStr">
@@ -24570,7 +24570,7 @@
       </c>
       <c r="I172" s="12" t="inlineStr">
         <is>
-          <t>1. Enrol user ID approver; submit.</t>
+          <t>1. Enrol the user ID of Andres Bautista (another approver); submit.</t>
         </is>
       </c>
       <c r="J172" s="12" t="inlineStr">
@@ -24580,7 +24580,7 @@
       </c>
       <c r="K172" s="12" t="inlineStr">
         <is>
-          <t>Refused. Message: User approver already exists</t>
+          <t>Refused. Message: User &lt;user ID&gt; already exists</t>
         </is>
       </c>
       <c r="L172" s="12" t="inlineStr">
@@ -24636,7 +24636,7 @@
       </c>
       <c r="F173" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G173" s="12" t="inlineStr">
@@ -24661,7 +24661,7 @@
       </c>
       <c r="K173" s="12" t="inlineStr">
         <is>
-          <t>Refused. Message: The user ID must be a letter followed by nine digits, for example a013000196</t>
+          <t>Refused. Message: The user ID must be a letter followed by nine digits, for example a999999999</t>
         </is>
       </c>
       <c r="L173" s="12" t="inlineStr">
@@ -24717,7 +24717,7 @@
       </c>
       <c r="F174" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G174" s="12" t="inlineStr">
@@ -24798,7 +24798,7 @@
       </c>
       <c r="F175" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G175" s="12" t="inlineStr">
@@ -24813,7 +24813,7 @@
       </c>
       <c r="I175" s="12" t="inlineStr">
         <is>
-          <t>1. Enrol a013000197 without a full name; submit.</t>
+          <t>1. Enrol a test user without a full name; submit.</t>
         </is>
       </c>
       <c r="J175" s="12" t="inlineStr">
@@ -24879,7 +24879,7 @@
       </c>
       <c r="F176" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G176" s="12" t="inlineStr">
@@ -24894,7 +24894,7 @@
       </c>
       <c r="I176" s="12" t="inlineStr">
         <is>
-          <t>1. Enrol a013000197 with no profile; submit.</t>
+          <t>1. Enrol a test user with no profile; submit.</t>
         </is>
       </c>
       <c r="J176" s="12" t="inlineStr">
@@ -24960,7 +24960,7 @@
       </c>
       <c r="F177" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G177" s="12" t="inlineStr">
@@ -25041,7 +25041,7 @@
       </c>
       <c r="F178" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G178" s="12" t="inlineStr">
@@ -25122,7 +25122,7 @@
       </c>
       <c r="F179" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G179" s="12" t="inlineStr">
@@ -25137,7 +25137,7 @@
       </c>
       <c r="I179" s="12" t="inlineStr">
         <is>
-          <t>1. Enrol a013000198 with the Windows ID of requestor; submit.</t>
+          <t>1. Enrol a test user with the Windows ID of Rhea Santiago (Requestor); submit.</t>
         </is>
       </c>
       <c r="J179" s="12" t="inlineStr">
@@ -25203,7 +25203,7 @@
       </c>
       <c r="F180" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G180" s="12" t="inlineStr">
@@ -25218,8 +25218,8 @@
       </c>
       <c r="I180" s="12" t="inlineStr">
         <is>
-          <t>1. Modify user; search the Marketing Team Lead test user; replace the profile with Processing Team Lead; submit; approve as uamapprover.
-2. As auditor run the User Access Audit Log.</t>
+          <t>1. Modify user; search the Marketing Team Lead test user; replace the profile with Processing Team Lead; submit; approve as Ulysses Abad (Approver).
+2. As Audrey Lim (Auditor) run the User Access Audit Log.</t>
         </is>
       </c>
       <c r="J180" s="12" t="inlineStr">
@@ -25285,7 +25285,7 @@
       </c>
       <c r="F181" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G181" s="12" t="inlineStr">
@@ -25366,7 +25366,7 @@
       </c>
       <c r="F182" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G182" s="12" t="inlineStr">
@@ -25447,7 +25447,7 @@
       </c>
       <c r="F183" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G183" s="12" t="inlineStr">
@@ -25528,7 +25528,7 @@
       </c>
       <c r="F184" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G184" s="12" t="inlineStr">
@@ -25543,7 +25543,7 @@
       </c>
       <c r="I184" s="12" t="inlineStr">
         <is>
-          <t>1. As requestor, Modify user requestor; add a profile; submit.</t>
+          <t>1. As Rhea Santiago (Requestor), Modify user Rhea Santiago (Requestor); add a profile; submit.</t>
         </is>
       </c>
       <c r="J184" s="12" t="inlineStr">
@@ -25609,7 +25609,7 @@
       </c>
       <c r="F185" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G185" s="12" t="inlineStr">
@@ -25624,8 +25624,8 @@
       </c>
       <c r="I185" s="12" t="inlineStr">
         <is>
-          <t>1. Deactivate user; search a013000196; reason Resigned; remarks; submit; approve as uamapprover.
-2. Log in as a013000196; as badmin run the User Access Report.</t>
+          <t>1. Deactivate user; search Isabel Navarro; reason Resigned; remarks; submit; approve as Ulysses Abad (Approver).
+2. Log in as Isabel Navarro; as Bea Villanueva (Business Administrator) run the User Access Report.</t>
         </is>
       </c>
       <c r="J185" s="12" t="inlineStr">
@@ -25773,7 +25773,7 @@
       </c>
       <c r="F187" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G187" s="12" t="inlineStr">
@@ -25854,7 +25854,7 @@
       </c>
       <c r="F188" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G188" s="12" t="inlineStr">
@@ -25915,7 +25915,7 @@
       </c>
       <c r="B189" s="12" t="inlineStr">
         <is>
-          <t>Reactivate a013000196</t>
+          <t>Reactivate Isabel Navarro</t>
         </is>
       </c>
       <c r="C189" s="12" t="inlineStr">
@@ -25935,7 +25935,7 @@
       </c>
       <c r="F189" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G189" s="12" t="inlineStr">
@@ -25950,8 +25950,8 @@
       </c>
       <c r="I189" s="12" t="inlineStr">
         <is>
-          <t>1. Reactivate user; search a013000196; remarks; submit; approve.
-2. Log in as a013000196.</t>
+          <t>1. Reactivate user; search Isabel Navarro; remarks; submit; approve.
+2. Log in as Isabel Navarro.</t>
         </is>
       </c>
       <c r="J189" s="12" t="inlineStr">
@@ -26017,7 +26017,7 @@
       </c>
       <c r="F190" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G190" s="12" t="inlineStr">
@@ -26098,7 +26098,7 @@
       </c>
       <c r="F191" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G191" s="12" t="inlineStr">
@@ -26113,7 +26113,7 @@
       </c>
       <c r="I191" s="12" t="inlineStr">
         <is>
-          <t>1. Submit a reactivation of requestor by a direct request.</t>
+          <t>1. Submit a reactivation of Rhea Santiago (Requestor) by a direct request.</t>
         </is>
       </c>
       <c r="J191" s="12" t="inlineStr">
@@ -26123,7 +26123,7 @@
       </c>
       <c r="K191" s="12" t="inlineStr">
         <is>
-          <t>Refused. Message: User requestor is already active</t>
+          <t>Refused. Message: User &lt;user ID&gt; is already active</t>
         </is>
       </c>
       <c r="L191" s="12" t="inlineStr">
@@ -26179,7 +26179,7 @@
       </c>
       <c r="F192" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G192" s="12" t="inlineStr">
@@ -26194,7 +26194,7 @@
       </c>
       <c r="I192" s="12" t="inlineStr">
         <is>
-          <t>1. New Request, Modify user for uamapprover2; open Approver.</t>
+          <t>1. New Request, Modify user for a second Approver; open Approver.</t>
         </is>
       </c>
       <c r="J192" s="12" t="inlineStr">
@@ -26204,7 +26204,7 @@
       </c>
       <c r="K192" s="12" t="inlineStr">
         <is>
-          <t>uamapprover and approver are listed; requestor and uamapprover2 are not.</t>
+          <t>Ulysses Abad (Approver) and Andres Bautista (another approver) are listed; Rhea Santiago (Requestor) and a second Approver are not.</t>
         </is>
       </c>
       <c r="L192" s="12" t="inlineStr">
@@ -26260,7 +26260,7 @@
       </c>
       <c r="F193" s="12" t="inlineStr">
         <is>
-          <t>uamapprover</t>
+          <t>Ulysses Abad</t>
         </is>
       </c>
       <c r="G193" s="12" t="inlineStr">
@@ -26275,8 +26275,8 @@
       </c>
       <c r="I193" s="12" t="inlineStr">
         <is>
-          <t>1. Submit a request to uamapprover.
-2. As uamapprover and as approver open the bell and Assigned to Me.</t>
+          <t>1. Submit a request to Ulysses Abad (Approver).
+2. As Ulysses Abad (Approver) and as Andres Bautista (another approver) open the bell and Assigned to Me.</t>
         </is>
       </c>
       <c r="J193" s="12" t="inlineStr">
@@ -26286,7 +26286,7 @@
       </c>
       <c r="K193" s="12" t="inlineStr">
         <is>
-          <t>uamapprover has the notification and the request; approver has neither.</t>
+          <t>Ulysses Abad (Approver) has the notification and the request; Andres Bautista (another approver) has neither.</t>
         </is>
       </c>
       <c r="L193" s="12" t="inlineStr">
@@ -26342,7 +26342,7 @@
       </c>
       <c r="F194" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G194" s="12" t="inlineStr">
@@ -26423,7 +26423,7 @@
       </c>
       <c r="F195" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G195" s="12" t="inlineStr">
@@ -26438,7 +26438,7 @@
       </c>
       <c r="I195" s="12" t="inlineStr">
         <is>
-          <t>1. Submit a Modify user request for uamapprover with approver uamapprover.</t>
+          <t>1. Submit a Modify user request for Ulysses Abad (Approver) with approver Ulysses Abad (Approver).</t>
         </is>
       </c>
       <c r="J195" s="12" t="inlineStr">
@@ -26448,7 +26448,7 @@
       </c>
       <c r="K195" s="12" t="inlineStr">
         <is>
-          <t>Refused. Message: uamapprover cannot approve this request</t>
+          <t>Refused. Message: &lt;user&gt; cannot approve this request</t>
         </is>
       </c>
       <c r="L195" s="12" t="inlineStr">
@@ -26504,7 +26504,7 @@
       </c>
       <c r="F196" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G196" s="12" t="inlineStr">
@@ -26585,7 +26585,7 @@
       </c>
       <c r="F197" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G197" s="12" t="inlineStr">
@@ -26666,7 +26666,7 @@
       </c>
       <c r="F198" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G198" s="12" t="inlineStr">
@@ -26747,7 +26747,7 @@
       </c>
       <c r="F199" s="12" t="inlineStr">
         <is>
-          <t>uamapprover</t>
+          <t>Ulysses Abad</t>
         </is>
       </c>
       <c r="G199" s="12" t="inlineStr">
@@ -26762,7 +26762,7 @@
       </c>
       <c r="I199" s="12" t="inlineStr">
         <is>
-          <t>1. As uamapprover send a direct request to re-submit the returned request.</t>
+          <t>1. As Ulysses Abad (Approver) send a direct request to re-submit the returned request.</t>
         </is>
       </c>
       <c r="J199" s="12" t="inlineStr">
@@ -26828,7 +26828,7 @@
       </c>
       <c r="F200" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G200" s="12" t="inlineStr">
@@ -26844,7 +26844,7 @@
       <c r="I200" s="12" t="inlineStr">
         <is>
           <t>1. Search the pending request; Cancel Request; reason; confirm.
-2. As uamapprover open My Approvals and the bell.</t>
+2. As Ulysses Abad (Approver) open My Approvals and the bell.</t>
         </is>
       </c>
       <c r="J200" s="12" t="inlineStr">
@@ -26854,7 +26854,7 @@
       </c>
       <c r="K200" s="12" t="inlineStr">
         <is>
-          <t>The request is CANCELLED with the reason; it is no longer in My Approvals; uamapprover is notified.</t>
+          <t>The request is CANCELLED with the reason; it is no longer in My Approvals; Ulysses Abad (Approver) is notified.</t>
         </is>
       </c>
       <c r="L200" s="12" t="inlineStr">
@@ -26910,7 +26910,7 @@
       </c>
       <c r="F201" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G201" s="12" t="inlineStr">
@@ -26992,7 +26992,7 @@
       </c>
       <c r="F202" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G202" s="12" t="inlineStr">
@@ -27073,7 +27073,7 @@
       </c>
       <c r="F203" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G203" s="12" t="inlineStr">
@@ -27154,7 +27154,7 @@
       </c>
       <c r="F204" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G204" s="12" t="inlineStr">
@@ -27169,7 +27169,7 @@
       </c>
       <c r="I204" s="12" t="inlineStr">
         <is>
-          <t>1. Filter by approver uamapprover and this month.</t>
+          <t>1. Filter by approver Ulysses Abad (Approver) and this month.</t>
         </is>
       </c>
       <c r="J204" s="12" t="inlineStr">
@@ -27179,7 +27179,7 @@
       </c>
       <c r="K204" s="12" t="inlineStr">
         <is>
-          <t>Only the requests of this month assigned to uamapprover.</t>
+          <t>Only the requests of this month assigned to Ulysses Abad (Approver).</t>
         </is>
       </c>
       <c r="L204" s="12" t="inlineStr">
@@ -27235,7 +27235,7 @@
       </c>
       <c r="F205" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G205" s="12" t="inlineStr">
@@ -27260,7 +27260,7 @@
       </c>
       <c r="K205" s="12" t="inlineStr">
         <is>
-          <t>Only requestor's requests, with number, type, change, dates, approver and status.</t>
+          <t>Only Rhea Santiago (Requestor)'s requests, with number, type, change, dates, approver and status.</t>
         </is>
       </c>
       <c r="L205" s="12" t="inlineStr">
@@ -27316,7 +27316,7 @@
       </c>
       <c r="F206" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G206" s="12" t="inlineStr">
@@ -27331,7 +27331,7 @@
       </c>
       <c r="I206" s="12" t="inlineStr">
         <is>
-          <t>1. As requestor open the address of a request of requestor2.</t>
+          <t>1. As Rhea Santiago (Requestor) open the address of a request of a second Requestor.</t>
         </is>
       </c>
       <c r="J206" s="12" t="inlineStr">
@@ -27397,7 +27397,7 @@
       </c>
       <c r="F207" s="12" t="inlineStr">
         <is>
-          <t>auditor</t>
+          <t>Audrey Lim</t>
         </is>
       </c>
       <c r="G207" s="12" t="inlineStr">
@@ -27412,7 +27412,7 @@
       </c>
       <c r="I207" s="12" t="inlineStr">
         <is>
-          <t>1. As auditor open Access Requests, tab All.</t>
+          <t>1. As Audrey Lim (Auditor) open Access Requests, tab All.</t>
         </is>
       </c>
       <c r="J207" s="12" t="inlineStr">
@@ -27478,7 +27478,7 @@
       </c>
       <c r="F208" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G208" s="12" t="inlineStr">
@@ -27559,7 +27559,7 @@
       </c>
       <c r="F209" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G209" s="12" t="inlineStr">
@@ -27640,7 +27640,7 @@
       </c>
       <c r="F210" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G210" s="12" t="inlineStr">
@@ -27655,8 +27655,8 @@
       </c>
       <c r="I210" s="12" t="inlineStr">
         <is>
-          <t>1. Download the template; attach the three-row file; check the validation report; remarks; Save Draft; choose uamapprover; Submit.
-2. As uamapprover approve the batch.</t>
+          <t>1. Download the template; attach the three-row file; check the validation report; remarks; Save Draft; choose Ulysses Abad (Approver); Submit.
+2. As Ulysses Abad (Approver) approve the batch.</t>
         </is>
       </c>
       <c r="J210" s="12" t="inlineStr">
@@ -27666,7 +27666,7 @@
       </c>
       <c r="K210" s="12" t="inlineStr">
         <is>
-          <t>A draft batch of three lines; after approval the three users a013000201 to a013000203 exist.</t>
+          <t>A draft batch of three lines; after approval the three new users exist.</t>
         </is>
       </c>
       <c r="L210" s="12" t="inlineStr">
@@ -27722,7 +27722,7 @@
       </c>
       <c r="F211" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G211" s="12" t="inlineStr">
@@ -27747,7 +27747,7 @@
       </c>
       <c r="K211" s="12" t="inlineStr">
         <is>
-          <t>The report lists the row with its error; no batch is created. Message: Row 2: User approver already exists</t>
+          <t>The report lists the row with its error; no batch is created. Message: Row 2: User &lt;user ID&gt; already exists</t>
         </is>
       </c>
       <c r="L211" s="12" t="inlineStr">
@@ -27803,7 +27803,7 @@
       </c>
       <c r="F212" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G212" s="12" t="inlineStr">
@@ -27884,7 +27884,7 @@
       </c>
       <c r="F213" s="12" t="inlineStr">
         <is>
-          <t>uamapprover</t>
+          <t>Ulysses Abad</t>
         </is>
       </c>
       <c r="G213" s="12" t="inlineStr">
@@ -27965,7 +27965,7 @@
       </c>
       <c r="F214" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G214" s="12" t="inlineStr">
@@ -28128,7 +28128,7 @@
       </c>
       <c r="F216" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G216" s="12" t="inlineStr">
@@ -28209,7 +28209,7 @@
       </c>
       <c r="F217" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G217" s="12" t="inlineStr">
@@ -28290,7 +28290,7 @@
       </c>
       <c r="F218" s="12" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>Samuel Cruz</t>
         </is>
       </c>
       <c r="G218" s="12" t="inlineStr">
@@ -28305,7 +28305,7 @@
       </c>
       <c r="I218" s="12" t="inlineStr">
         <is>
-          <t>1. Run the job on the date; as admin open the bell.</t>
+          <t>1. Run the job on the date; as Samuel Cruz (System Administrator) open the bell.</t>
         </is>
       </c>
       <c r="J218" s="12" t="inlineStr">
@@ -28371,7 +28371,7 @@
       </c>
       <c r="F219" s="12" t="inlineStr">
         <is>
-          <t>uamapprover</t>
+          <t>Ulysses Abad</t>
         </is>
       </c>
       <c r="G219" s="12" t="inlineStr">
@@ -28452,7 +28452,7 @@
       </c>
       <c r="F220" s="12" t="inlineStr">
         <is>
-          <t>uamapprover</t>
+          <t>Ulysses Abad</t>
         </is>
       </c>
       <c r="G220" s="12" t="inlineStr">
@@ -28533,7 +28533,7 @@
       </c>
       <c r="F221" s="12" t="inlineStr">
         <is>
-          <t>approver</t>
+          <t>Andres Bautista</t>
         </is>
       </c>
       <c r="G221" s="12" t="inlineStr">
@@ -28548,7 +28548,7 @@
       </c>
       <c r="I221" s="12" t="inlineStr">
         <is>
-          <t>1. As approver open My Approvals.</t>
+          <t>1. As Andres Bautista (another approver) open My Approvals.</t>
         </is>
       </c>
       <c r="J221" s="12" t="inlineStr">
@@ -28558,7 +28558,7 @@
       </c>
       <c r="K221" s="12" t="inlineStr">
         <is>
-          <t>The request assigned to uamapprover is not listed.</t>
+          <t>The request assigned to Ulysses Abad (Approver) is not listed.</t>
         </is>
       </c>
       <c r="L221" s="12" t="inlineStr">
@@ -28614,7 +28614,7 @@
       </c>
       <c r="F222" s="12" t="inlineStr">
         <is>
-          <t>uamapprover</t>
+          <t>Ulysses Abad</t>
         </is>
       </c>
       <c r="G222" s="12" t="inlineStr">
@@ -28695,7 +28695,7 @@
       </c>
       <c r="F223" s="12" t="inlineStr">
         <is>
-          <t>uamapprover</t>
+          <t>Ulysses Abad</t>
         </is>
       </c>
       <c r="G223" s="12" t="inlineStr">
@@ -28776,7 +28776,7 @@
       </c>
       <c r="F224" s="12" t="inlineStr">
         <is>
-          <t>uamapprover</t>
+          <t>Ulysses Abad</t>
         </is>
       </c>
       <c r="G224" s="12" t="inlineStr">
@@ -28786,12 +28786,12 @@
       </c>
       <c r="H224" s="12" t="inlineStr">
         <is>
-          <t>A request about uamapprover2 with the any-approver setting true.</t>
+          <t>A request about a second Approver with the any-approver setting true.</t>
         </is>
       </c>
       <c r="I224" s="12" t="inlineStr">
         <is>
-          <t>1. As uamapprover2 click Approve and Apply.</t>
+          <t>1. As a second Approver click Approve and Apply.</t>
         </is>
       </c>
       <c r="J224" s="12" t="inlineStr">
@@ -28857,7 +28857,7 @@
       </c>
       <c r="F225" s="12" t="inlineStr">
         <is>
-          <t>uamapprover</t>
+          <t>Ulysses Abad</t>
         </is>
       </c>
       <c r="G225" s="12" t="inlineStr">
@@ -28882,7 +28882,7 @@
       </c>
       <c r="K225" s="12" t="inlineStr">
         <is>
-          <t>The approval is refused because the user now exists; nothing is applied. Message: User a013000199 already exists</t>
+          <t>The approval is refused because the user now exists; nothing is applied. Message: User &lt;user ID&gt; already exists</t>
         </is>
       </c>
       <c r="L225" s="12" t="inlineStr">
@@ -28938,7 +28938,7 @@
       </c>
       <c r="F226" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G226" s="12" t="inlineStr">
@@ -28953,8 +28953,8 @@
       </c>
       <c r="I226" s="12" t="inlineStr">
         <is>
-          <t>1. As uamapprover enter the reason "Profile not needed"; Reject.
-2. As requestor open the request.</t>
+          <t>1. As Ulysses Abad (Approver) enter the reason "Profile not needed"; Reject.
+2. As Rhea Santiago (Requestor) open the request.</t>
         </is>
       </c>
       <c r="J226" s="12" t="inlineStr">
@@ -28964,7 +28964,7 @@
       </c>
       <c r="K226" s="12" t="inlineStr">
         <is>
-          <t>REJECTED with the reason; nothing changed on the user; requestor is notified.</t>
+          <t>REJECTED with the reason; nothing changed on the user; Rhea Santiago (Requestor) is notified.</t>
         </is>
       </c>
       <c r="L226" s="12" t="inlineStr">
@@ -29020,7 +29020,7 @@
       </c>
       <c r="F227" s="12" t="inlineStr">
         <is>
-          <t>uamapprover</t>
+          <t>Ulysses Abad</t>
         </is>
       </c>
       <c r="G227" s="12" t="inlineStr">
@@ -29101,7 +29101,7 @@
       </c>
       <c r="F228" s="12" t="inlineStr">
         <is>
-          <t>uamapprover</t>
+          <t>Ulysses Abad</t>
         </is>
       </c>
       <c r="G228" s="12" t="inlineStr">
@@ -29182,7 +29182,7 @@
       </c>
       <c r="F229" s="12" t="inlineStr">
         <is>
-          <t>uamapprover</t>
+          <t>Ulysses Abad</t>
         </is>
       </c>
       <c r="G229" s="12" t="inlineStr">
@@ -29207,7 +29207,7 @@
       </c>
       <c r="K229" s="12" t="inlineStr">
         <is>
-          <t>RETURNED; remarks in the history; requestor notified.</t>
+          <t>RETURNED; remarks in the history; Rhea Santiago (Requestor) notified.</t>
         </is>
       </c>
       <c r="L229" s="12" t="inlineStr">
@@ -29263,7 +29263,7 @@
       </c>
       <c r="F230" s="12" t="inlineStr">
         <is>
-          <t>uamapprover</t>
+          <t>Ulysses Abad</t>
         </is>
       </c>
       <c r="G230" s="12" t="inlineStr">
@@ -29344,7 +29344,7 @@
       </c>
       <c r="F231" s="12" t="inlineStr">
         <is>
-          <t>secapprover</t>
+          <t>Selina Reyes</t>
         </is>
       </c>
       <c r="G231" s="12" t="inlineStr">
@@ -29359,8 +29359,8 @@
       </c>
       <c r="I231" s="12" t="inlineStr">
         <is>
-          <t>1. As requestor submit a Modify user adding System Administrator; as uamapprover approve.
-2. As secapprover open tab Second Approval; approve.</t>
+          <t>1. As Rhea Santiago (Requestor) submit a Modify user adding System Administrator; as Ulysses Abad (Approver) approve.
+2. As Selina Reyes (Second Approver) open tab Second Approval; approve.</t>
         </is>
       </c>
       <c r="J231" s="12" t="inlineStr">
@@ -29426,7 +29426,7 @@
       </c>
       <c r="F232" s="12" t="inlineStr">
         <is>
-          <t>secapprover</t>
+          <t>Selina Reyes</t>
         </is>
       </c>
       <c r="G232" s="12" t="inlineStr">
@@ -29441,7 +29441,7 @@
       </c>
       <c r="I232" s="12" t="inlineStr">
         <is>
-          <t>1. Submit a request at 21:00 (test clock); approve as uamapprover.</t>
+          <t>1. Submit a request at 21:00 (test clock); approve as Ulysses Abad (Approver).</t>
         </is>
       </c>
       <c r="J232" s="12" t="inlineStr">
@@ -29507,7 +29507,7 @@
       </c>
       <c r="F233" s="12" t="inlineStr">
         <is>
-          <t>secapprover</t>
+          <t>Selina Reyes</t>
         </is>
       </c>
       <c r="G233" s="12" t="inlineStr">
@@ -29588,7 +29588,7 @@
       </c>
       <c r="F234" s="12" t="inlineStr">
         <is>
-          <t>secapprover</t>
+          <t>Selina Reyes</t>
         </is>
       </c>
       <c r="G234" s="12" t="inlineStr">
@@ -29669,7 +29669,7 @@
       </c>
       <c r="F235" s="12" t="inlineStr">
         <is>
-          <t>secapprover</t>
+          <t>Selina Reyes</t>
         </is>
       </c>
       <c r="G235" s="12" t="inlineStr">
@@ -29684,7 +29684,7 @@
       </c>
       <c r="I235" s="12" t="inlineStr">
         <is>
-          <t>1. As secapprover return a Pending Second Approval request with remarks.</t>
+          <t>1. As Selina Reyes (Second Approver) return a Pending Second Approval request with remarks.</t>
         </is>
       </c>
       <c r="J235" s="12" t="inlineStr">
@@ -29750,7 +29750,7 @@
       </c>
       <c r="F236" s="12" t="inlineStr">
         <is>
-          <t>badmin</t>
+          <t>Bea Villanueva</t>
         </is>
       </c>
       <c r="G236" s="12" t="inlineStr">
@@ -29765,8 +29765,8 @@
       </c>
       <c r="I236" s="12" t="inlineStr">
         <is>
-          <t>1. New Group Profile Request, Create; code PROC_TL2; name; privilege Standard; pick permissions by area and action; approvers uamapprover then approver; remarks; submit.
-2. Approve as uamapprover, then as approver.</t>
+          <t>1. New Group Profile Request, Create; code PROC_TL2; name; privilege Standard; pick permissions by area and action; approvers Ulysses Abad (Approver) then Andres Bautista (another approver); remarks; submit.
+2. Approve as Ulysses Abad (Approver), then as Andres Bautista (another approver).</t>
         </is>
       </c>
       <c r="J236" s="12" t="inlineStr">
@@ -29832,7 +29832,7 @@
       </c>
       <c r="F237" s="12" t="inlineStr">
         <is>
-          <t>badmin</t>
+          <t>Bea Villanueva</t>
         </is>
       </c>
       <c r="G237" s="12" t="inlineStr">
@@ -29913,7 +29913,7 @@
       </c>
       <c r="F238" s="12" t="inlineStr">
         <is>
-          <t>badmin</t>
+          <t>Bea Villanueva</t>
         </is>
       </c>
       <c r="G238" s="12" t="inlineStr">
@@ -29994,7 +29994,7 @@
       </c>
       <c r="F239" s="12" t="inlineStr">
         <is>
-          <t>badmin</t>
+          <t>Bea Villanueva</t>
         </is>
       </c>
       <c r="G239" s="12" t="inlineStr">
@@ -30075,7 +30075,7 @@
       </c>
       <c r="F240" s="12" t="inlineStr">
         <is>
-          <t>badmin</t>
+          <t>Bea Villanueva</t>
         </is>
       </c>
       <c r="G240" s="12" t="inlineStr">
@@ -30156,7 +30156,7 @@
       </c>
       <c r="F241" s="12" t="inlineStr">
         <is>
-          <t>badmin</t>
+          <t>Bea Villanueva</t>
         </is>
       </c>
       <c r="G241" s="12" t="inlineStr">
@@ -30237,7 +30237,7 @@
       </c>
       <c r="F242" s="12" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>Samuel Cruz</t>
         </is>
       </c>
       <c r="G242" s="12" t="inlineStr">
@@ -30253,7 +30253,7 @@
       <c r="I242" s="12" t="inlineStr">
         <is>
           <t>1. Modify profile Marketing Team Lead; add the report permission; remove one other permission; approvers; submit; approve.
-2. As admin implement it; open Roles &amp; Permissions.</t>
+2. As Samuel Cruz (System Administrator) implement it; open Roles &amp; Permissions.</t>
         </is>
       </c>
       <c r="J242" s="12" t="inlineStr">
@@ -30319,7 +30319,7 @@
       </c>
       <c r="F243" s="12" t="inlineStr">
         <is>
-          <t>badmin</t>
+          <t>Bea Villanueva</t>
         </is>
       </c>
       <c r="G243" s="12" t="inlineStr">
@@ -30400,7 +30400,7 @@
       </c>
       <c r="F244" s="12" t="inlineStr">
         <is>
-          <t>badmin</t>
+          <t>Bea Villanueva</t>
         </is>
       </c>
       <c r="G244" s="12" t="inlineStr">
@@ -30481,7 +30481,7 @@
       </c>
       <c r="F245" s="12" t="inlineStr">
         <is>
-          <t>badmin</t>
+          <t>Bea Villanueva</t>
         </is>
       </c>
       <c r="G245" s="12" t="inlineStr">
@@ -30562,7 +30562,7 @@
       </c>
       <c r="F246" s="12" t="inlineStr">
         <is>
-          <t>badmin</t>
+          <t>Bea Villanueva</t>
         </is>
       </c>
       <c r="G246" s="12" t="inlineStr">
@@ -30643,7 +30643,7 @@
       </c>
       <c r="F247" s="12" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>Samuel Cruz</t>
         </is>
       </c>
       <c r="G247" s="12" t="inlineStr">
@@ -30724,7 +30724,7 @@
       </c>
       <c r="F248" s="12" t="inlineStr">
         <is>
-          <t>badmin</t>
+          <t>Bea Villanueva</t>
         </is>
       </c>
       <c r="G248" s="12" t="inlineStr">
@@ -30739,8 +30739,8 @@
       </c>
       <c r="I248" s="12" t="inlineStr">
         <is>
-          <t>1. Deactivate UAT_HIGH; approvers; submit; approve; admin implements.
-2. A member of UAT_HIGH clicks a screen of that profile; requestor opens New Request.</t>
+          <t>1. Deactivate UAT_HIGH; approvers; submit; approve; Samuel Cruz (System Administrator) implements.
+2. A member of UAT_HIGH clicks a screen of that profile; Rhea Santiago (Requestor) opens New Request.</t>
         </is>
       </c>
       <c r="J248" s="12" t="inlineStr">
@@ -30806,7 +30806,7 @@
       </c>
       <c r="F249" s="12" t="inlineStr">
         <is>
-          <t>badmin</t>
+          <t>Bea Villanueva</t>
         </is>
       </c>
       <c r="G249" s="12" t="inlineStr">
@@ -30887,7 +30887,7 @@
       </c>
       <c r="F250" s="12" t="inlineStr">
         <is>
-          <t>badmin</t>
+          <t>Bea Villanueva</t>
         </is>
       </c>
       <c r="G250" s="12" t="inlineStr">
@@ -30968,7 +30968,7 @@
       </c>
       <c r="F251" s="12" t="inlineStr">
         <is>
-          <t>badmin</t>
+          <t>Bea Villanueva</t>
         </is>
       </c>
       <c r="G251" s="12" t="inlineStr">
@@ -31049,7 +31049,7 @@
       </c>
       <c r="F252" s="12" t="inlineStr">
         <is>
-          <t>badmin</t>
+          <t>Bea Villanueva</t>
         </is>
       </c>
       <c r="G252" s="12" t="inlineStr">
@@ -31064,7 +31064,7 @@
       </c>
       <c r="I252" s="12" t="inlineStr">
         <is>
-          <t>1. Reactivate UAT_HIGH; approvers; submit; approve; admin implements.
+          <t>1. Reactivate UAT_HIGH; approvers; submit; approve; Samuel Cruz (System Administrator) implements.
 2. A member opens a screen of UAT_HIGH.</t>
         </is>
       </c>
@@ -31131,7 +31131,7 @@
       </c>
       <c r="F253" s="12" t="inlineStr">
         <is>
-          <t>badmin</t>
+          <t>Bea Villanueva</t>
         </is>
       </c>
       <c r="G253" s="12" t="inlineStr">
@@ -31212,7 +31212,7 @@
       </c>
       <c r="F254" s="12" t="inlineStr">
         <is>
-          <t>approver</t>
+          <t>Andres Bautista</t>
         </is>
       </c>
       <c r="G254" s="12" t="inlineStr">
@@ -31227,8 +31227,8 @@
       </c>
       <c r="I254" s="12" t="inlineStr">
         <is>
-          <t>1. badmin submits with approvers uamapprover then approver; approver checks the bell.
-2. uamapprover approves; approver checks again.</t>
+          <t>1. Bea Villanueva (Business Administrator) submits with approvers Ulysses Abad (Approver) then Andres Bautista (another approver); Andres Bautista (another approver) checks the bell.
+2. Ulysses Abad (Approver) approves; Andres Bautista (another approver) checks again.</t>
         </is>
       </c>
       <c r="J254" s="12" t="inlineStr">
@@ -31238,7 +31238,7 @@
       </c>
       <c r="K254" s="12" t="inlineStr">
         <is>
-          <t>approver is notified only after uamapprover approves.</t>
+          <t>Andres Bautista (another approver) is notified only after Ulysses Abad (Approver) approves.</t>
         </is>
       </c>
       <c r="L254" s="12" t="inlineStr">
@@ -31294,7 +31294,7 @@
       </c>
       <c r="F255" s="12" t="inlineStr">
         <is>
-          <t>uamapprover</t>
+          <t>Ulysses Abad</t>
         </is>
       </c>
       <c r="G255" s="12" t="inlineStr">
@@ -31309,7 +31309,7 @@
       </c>
       <c r="I255" s="12" t="inlineStr">
         <is>
-          <t>1. uamapprover rejects with a reason.</t>
+          <t>1. Ulysses Abad (Approver) rejects with a reason.</t>
         </is>
       </c>
       <c r="J255" s="12" t="inlineStr">
@@ -31319,7 +31319,7 @@
       </c>
       <c r="K255" s="12" t="inlineStr">
         <is>
-          <t>REJECTED; approver is never asked.</t>
+          <t>REJECTED; Andres Bautista (another approver) is never asked.</t>
         </is>
       </c>
       <c r="L255" s="12" t="inlineStr">
@@ -31375,7 +31375,7 @@
       </c>
       <c r="F256" s="12" t="inlineStr">
         <is>
-          <t>badmin</t>
+          <t>Bea Villanueva</t>
         </is>
       </c>
       <c r="G256" s="12" t="inlineStr">
@@ -31390,7 +31390,7 @@
       </c>
       <c r="I256" s="12" t="inlineStr">
         <is>
-          <t>1. approver returns; badmin corrects and re-submits.</t>
+          <t>1. Andres Bautista (another approver) returns; Bea Villanueva (Business Administrator) corrects and re-submits.</t>
         </is>
       </c>
       <c r="J256" s="12" t="inlineStr">
@@ -31400,7 +31400,7 @@
       </c>
       <c r="K256" s="12" t="inlineStr">
         <is>
-          <t>The request goes back to uamapprover first.</t>
+          <t>The request goes back to Ulysses Abad (Approver) first.</t>
         </is>
       </c>
       <c r="L256" s="12" t="inlineStr">
@@ -31456,7 +31456,7 @@
       </c>
       <c r="F257" s="12" t="inlineStr">
         <is>
-          <t>badmin</t>
+          <t>Bea Villanueva</t>
         </is>
       </c>
       <c r="G257" s="12" t="inlineStr">
@@ -31537,7 +31537,7 @@
       </c>
       <c r="F258" s="12" t="inlineStr">
         <is>
-          <t>badmin</t>
+          <t>Bea Villanueva</t>
         </is>
       </c>
       <c r="G258" s="12" t="inlineStr">
@@ -31552,7 +31552,7 @@
       </c>
       <c r="I258" s="12" t="inlineStr">
         <is>
-          <t>1. Add uamapprover twice.</t>
+          <t>1. Add Ulysses Abad (Approver) twice.</t>
         </is>
       </c>
       <c r="J258" s="12" t="inlineStr">
@@ -31562,7 +31562,7 @@
       </c>
       <c r="K258" s="12" t="inlineStr">
         <is>
-          <t>Refused. Message: uamapprover is already an approver of this request</t>
+          <t>Refused. Message: &lt;user&gt; is already an approver of this request</t>
         </is>
       </c>
       <c r="L258" s="12" t="inlineStr">
@@ -31618,7 +31618,7 @@
       </c>
       <c r="F259" s="12" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>Samuel Cruz</t>
         </is>
       </c>
       <c r="G259" s="12" t="inlineStr">
@@ -31643,7 +31643,7 @@
       </c>
       <c r="K259" s="12" t="inlineStr">
         <is>
-          <t>The profile exists; IMPLEMENTED; badmin notified.</t>
+          <t>The profile exists; IMPLEMENTED; Bea Villanueva (Business Administrator) notified.</t>
         </is>
       </c>
       <c r="L259" s="12" t="inlineStr">
@@ -31699,7 +31699,7 @@
       </c>
       <c r="F260" s="12" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>Samuel Cruz</t>
         </is>
       </c>
       <c r="G260" s="12" t="inlineStr">
@@ -31780,7 +31780,7 @@
       </c>
       <c r="F261" s="12" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>Samuel Cruz</t>
         </is>
       </c>
       <c r="G261" s="12" t="inlineStr">
@@ -31861,7 +31861,7 @@
       </c>
       <c r="F262" s="12" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>Samuel Cruz</t>
         </is>
       </c>
       <c r="G262" s="12" t="inlineStr">
@@ -31942,7 +31942,7 @@
       </c>
       <c r="F263" s="12" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>Samuel Cruz</t>
         </is>
       </c>
       <c r="G263" s="12" t="inlineStr">
@@ -32023,7 +32023,7 @@
       </c>
       <c r="F264" s="12" t="inlineStr">
         <is>
-          <t>badmin</t>
+          <t>Bea Villanueva</t>
         </is>
       </c>
       <c r="G264" s="12" t="inlineStr">
@@ -32038,7 +32038,7 @@
       </c>
       <c r="I264" s="12" t="inlineStr">
         <is>
-          <t>1. As badmin raise a Modify user request.</t>
+          <t>1. As Bea Villanueva (Business Administrator) raise a Modify user request.</t>
         </is>
       </c>
       <c r="J264" s="12" t="inlineStr">
@@ -32104,7 +32104,7 @@
       </c>
       <c r="F265" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G265" s="12" t="inlineStr">
@@ -32119,7 +32119,7 @@
       </c>
       <c r="I265" s="12" t="inlineStr">
         <is>
-          <t>1. As requestor open My Approvals; send a direct request to approve a pending request.</t>
+          <t>1. As Rhea Santiago (Requestor) open My Approvals; send a direct request to approve a pending request.</t>
         </is>
       </c>
       <c r="J265" s="12" t="inlineStr">
@@ -32185,7 +32185,7 @@
       </c>
       <c r="F266" s="12" t="inlineStr">
         <is>
-          <t>badmin</t>
+          <t>Bea Villanueva</t>
         </is>
       </c>
       <c r="G266" s="12" t="inlineStr">
@@ -32266,7 +32266,7 @@
       </c>
       <c r="F267" s="12" t="inlineStr">
         <is>
-          <t>uamapprover</t>
+          <t>Ulysses Abad</t>
         </is>
       </c>
       <c r="G267" s="12" t="inlineStr">
@@ -32281,7 +32281,7 @@
       </c>
       <c r="I267" s="12" t="inlineStr">
         <is>
-          <t>1. As uamapprover (no the cancel permission) open an own request; send a direct request to cancel it.</t>
+          <t>1. As Ulysses Abad (Approver) (no the cancel permission) open an own request; send a direct request to cancel it.</t>
         </is>
       </c>
       <c r="J267" s="12" t="inlineStr">
@@ -32347,7 +32347,7 @@
       </c>
       <c r="F268" s="12" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>Samuel Cruz</t>
         </is>
       </c>
       <c r="G268" s="12" t="inlineStr">
@@ -32428,7 +32428,7 @@
       </c>
       <c r="F269" s="12" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>Samuel Cruz</t>
         </is>
       </c>
       <c r="G269" s="12" t="inlineStr">
@@ -32509,7 +32509,7 @@
       </c>
       <c r="F270" s="12" t="inlineStr">
         <is>
-          <t>auditor</t>
+          <t>Audrey Lim</t>
         </is>
       </c>
       <c r="G270" s="12" t="inlineStr">
@@ -32524,7 +32524,7 @@
       </c>
       <c r="I270" s="12" t="inlineStr">
         <is>
-          <t>1. As admin unlock the locked user; as auditor run the User Access Audit Log.</t>
+          <t>1. As Samuel Cruz (System Administrator) unlock the locked user; as Audrey Lim (Auditor) run the User Access Audit Log.</t>
         </is>
       </c>
       <c r="J270" s="12" t="inlineStr">
@@ -32534,7 +32534,7 @@
       </c>
       <c r="K270" s="12" t="inlineStr">
         <is>
-          <t>The unlock is listed with admin and the time.</t>
+          <t>The unlock is listed with Samuel Cruz (System Administrator) and the time.</t>
         </is>
       </c>
       <c r="L270" s="12" t="inlineStr">
@@ -32590,7 +32590,7 @@
       </c>
       <c r="F271" s="12" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>Samuel Cruz</t>
         </is>
       </c>
       <c r="G271" s="12" t="inlineStr">
@@ -32605,7 +32605,7 @@
       </c>
       <c r="I271" s="12" t="inlineStr">
         <is>
-          <t>1. As admin edit the own user and add a role.</t>
+          <t>1. As Samuel Cruz (System Administrator) edit the own user and add a role.</t>
         </is>
       </c>
       <c r="J271" s="12" t="inlineStr">
@@ -32671,7 +32671,7 @@
       </c>
       <c r="F272" s="12" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>Samuel Cruz</t>
         </is>
       </c>
       <c r="G272" s="12" t="inlineStr">
@@ -32752,7 +32752,7 @@
       </c>
       <c r="F273" s="12" t="inlineStr">
         <is>
-          <t>badmin</t>
+          <t>Bea Villanueva</t>
         </is>
       </c>
       <c r="G273" s="12" t="inlineStr">
@@ -32767,9 +32767,9 @@
       </c>
       <c r="I273" s="12" t="inlineStr">
         <is>
-          <t>1. As badmin add a rule on Marketing Account Officer and Marketing Team Lead with a reason.
-2. As infosec authorise it (Separation of Duties or My Approvals).
-3. As requestor enrol a new user with both profiles.</t>
+          <t>1. As Bea Villanueva (Business Administrator) add a rule on Marketing Account Officer and Marketing Team Lead with a reason.
+2. As the Information Security Officer authorise it (Separation of Duties or My Approvals).
+3. As Rhea Santiago (Requestor) enrol a new user with both profiles.</t>
         </is>
       </c>
       <c r="J273" s="12" t="inlineStr">
@@ -32835,7 +32835,7 @@
       </c>
       <c r="F274" s="12" t="inlineStr">
         <is>
-          <t>badmin</t>
+          <t>Bea Villanueva</t>
         </is>
       </c>
       <c r="G274" s="12" t="inlineStr">
@@ -32850,7 +32850,7 @@
       </c>
       <c r="I274" s="12" t="inlineStr">
         <is>
-          <t>1. As badmin try to authorise the rule just created (direct request).</t>
+          <t>1. As Bea Villanueva (Business Administrator) try to authorise the rule just created (direct request).</t>
         </is>
       </c>
       <c r="J274" s="12" t="inlineStr">
@@ -32916,7 +32916,7 @@
       </c>
       <c r="F275" s="12" t="inlineStr">
         <is>
-          <t>badmin</t>
+          <t>Bea Villanueva</t>
         </is>
       </c>
       <c r="G275" s="12" t="inlineStr">
@@ -32997,7 +32997,7 @@
       </c>
       <c r="F276" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G276" s="12" t="inlineStr">
@@ -33078,7 +33078,7 @@
       </c>
       <c r="F277" s="12" t="inlineStr">
         <is>
-          <t>infosec</t>
+          <t>Information Security Officer</t>
         </is>
       </c>
       <c r="G277" s="12" t="inlineStr">
@@ -33093,7 +33093,7 @@
       </c>
       <c r="I277" s="12" t="inlineStr">
         <is>
-          <t>1. As badmin deactivate the rule; as infosec reject, then after a new deactivation authorise.</t>
+          <t>1. As Bea Villanueva (Business Administrator) deactivate the rule; as the Information Security Officer reject, then after a new deactivation authorise.</t>
         </is>
       </c>
       <c r="J277" s="12" t="inlineStr">
@@ -33159,7 +33159,7 @@
       </c>
       <c r="F278" s="12" t="inlineStr">
         <is>
-          <t>badmin</t>
+          <t>Bea Villanueva</t>
         </is>
       </c>
       <c r="G278" s="12" t="inlineStr">
@@ -33174,8 +33174,8 @@
       </c>
       <c r="I278" s="12" t="inlineStr">
         <is>
-          <t>1. As badmin add a rule of the type Two permissions not held together on two permissions with a reason; as infosec authorise it.
-2. As badmin raise a group-profile request that gives one profile both permissions.</t>
+          <t>1. As Bea Villanueva (Business Administrator) add a rule of the type Two permissions not held together on two permissions with a reason; as the Information Security Officer authorise it.
+2. As Bea Villanueva (Business Administrator) raise a group-profile request that gives one profile both permissions.</t>
         </is>
       </c>
       <c r="J278" s="12" t="inlineStr">
@@ -33241,7 +33241,7 @@
       </c>
       <c r="F279" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G279" s="12" t="inlineStr">
@@ -33322,7 +33322,7 @@
       </c>
       <c r="F280" s="12" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>Samuel Cruz</t>
         </is>
       </c>
       <c r="G280" s="12" t="inlineStr">
@@ -33337,8 +33337,8 @@
       </c>
       <c r="I280" s="12" t="inlineStr">
         <is>
-          <t>1. As admin set the minimum password age to 2.
-2. As infosec open the setting and approve.</t>
+          <t>1. As Samuel Cruz (System Administrator) set the minimum password age to 2.
+2. As the Information Security Officer open the setting and approve.</t>
         </is>
       </c>
       <c r="J280" s="12" t="inlineStr">
@@ -33404,7 +33404,7 @@
       </c>
       <c r="F281" s="12" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>Samuel Cruz</t>
         </is>
       </c>
       <c r="G281" s="12" t="inlineStr">
@@ -33419,7 +33419,7 @@
       </c>
       <c r="I281" s="12" t="inlineStr">
         <is>
-          <t>1. As admin send a direct request to approve the own change.</t>
+          <t>1. As Samuel Cruz (System Administrator) send a direct request to approve the own change.</t>
         </is>
       </c>
       <c r="J281" s="12" t="inlineStr">
@@ -33485,7 +33485,7 @@
       </c>
       <c r="F282" s="12" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>Samuel Cruz</t>
         </is>
       </c>
       <c r="G282" s="12" t="inlineStr">
@@ -33500,7 +33500,7 @@
       </c>
       <c r="I282" s="12" t="inlineStr">
         <is>
-          <t>1. As admin change the same setting again before the decision.</t>
+          <t>1. As Samuel Cruz (System Administrator) change the same setting again before the decision.</t>
         </is>
       </c>
       <c r="J282" s="12" t="inlineStr">
@@ -33566,7 +33566,7 @@
       </c>
       <c r="F283" s="12" t="inlineStr">
         <is>
-          <t>infosec</t>
+          <t>Information Security Officer</t>
         </is>
       </c>
       <c r="G283" s="12" t="inlineStr">
@@ -33581,7 +33581,7 @@
       </c>
       <c r="I283" s="12" t="inlineStr">
         <is>
-          <t>1. As admin set the emergency role edit to true; as infosec reject.</t>
+          <t>1. As Samuel Cruz (System Administrator) set the emergency role edit to true; as the Information Security Officer reject.</t>
         </is>
       </c>
       <c r="J283" s="12" t="inlineStr">
@@ -33647,7 +33647,7 @@
       </c>
       <c r="F284" s="12" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>Samuel Cruz</t>
         </is>
       </c>
       <c r="G284" s="12" t="inlineStr">
@@ -33662,7 +33662,7 @@
       </c>
       <c r="I284" s="12" t="inlineStr">
         <is>
-          <t>1. As admin change REPORT_FOOTER_TEXT.</t>
+          <t>1. As Samuel Cruz (System Administrator) change REPORT_FOOTER_TEXT.</t>
         </is>
       </c>
       <c r="J284" s="12" t="inlineStr">
@@ -33728,7 +33728,7 @@
       </c>
       <c r="F285" s="12" t="inlineStr">
         <is>
-          <t>badmin</t>
+          <t>Bea Villanueva</t>
         </is>
       </c>
       <c r="G285" s="12" t="inlineStr">
@@ -33743,7 +33743,7 @@
       </c>
       <c r="I285" s="12" t="inlineStr">
         <is>
-          <t>1. Run the User Access Report as of today for a013000196.</t>
+          <t>1. Run the User Access Report as of today for Isabel Navarro.</t>
         </is>
       </c>
       <c r="J285" s="12" t="inlineStr">
@@ -33809,7 +33809,7 @@
       </c>
       <c r="F286" s="12" t="inlineStr">
         <is>
-          <t>badmin</t>
+          <t>Bea Villanueva</t>
         </is>
       </c>
       <c r="G286" s="12" t="inlineStr">
@@ -33890,7 +33890,7 @@
       </c>
       <c r="F287" s="12" t="inlineStr">
         <is>
-          <t>badmin</t>
+          <t>Bea Villanueva</t>
         </is>
       </c>
       <c r="G287" s="12" t="inlineStr">
@@ -33971,7 +33971,7 @@
       </c>
       <c r="F288" s="12" t="inlineStr">
         <is>
-          <t>badmin</t>
+          <t>Bea Villanueva</t>
         </is>
       </c>
       <c r="G288" s="12" t="inlineStr">
@@ -34052,7 +34052,7 @@
       </c>
       <c r="F289" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G289" s="12" t="inlineStr">
@@ -34067,7 +34067,7 @@
       </c>
       <c r="I289" s="12" t="inlineStr">
         <is>
-          <t>1. As requestor open User Access Reports.</t>
+          <t>1. As Rhea Santiago (Requestor) open User Access Reports.</t>
         </is>
       </c>
       <c r="J289" s="12" t="inlineStr">
@@ -34133,7 +34133,7 @@
       </c>
       <c r="F290" s="12" t="inlineStr">
         <is>
-          <t>badmin</t>
+          <t>Bea Villanueva</t>
         </is>
       </c>
       <c r="G290" s="12" t="inlineStr">
@@ -34214,7 +34214,7 @@
       </c>
       <c r="F291" s="12" t="inlineStr">
         <is>
-          <t>badmin</t>
+          <t>Bea Villanueva</t>
         </is>
       </c>
       <c r="G291" s="12" t="inlineStr">
@@ -34295,7 +34295,7 @@
       </c>
       <c r="F292" s="12" t="inlineStr">
         <is>
-          <t>auditor</t>
+          <t>Audrey Lim</t>
         </is>
       </c>
       <c r="G292" s="12" t="inlineStr">
@@ -34376,7 +34376,7 @@
       </c>
       <c r="F293" s="12" t="inlineStr">
         <is>
-          <t>auditor</t>
+          <t>Audrey Lim</t>
         </is>
       </c>
       <c r="G293" s="12" t="inlineStr">
@@ -34457,7 +34457,7 @@
       </c>
       <c r="F294" s="12" t="inlineStr">
         <is>
-          <t>auditor</t>
+          <t>Audrey Lim</t>
         </is>
       </c>
       <c r="G294" s="12" t="inlineStr">
@@ -34538,7 +34538,7 @@
       </c>
       <c r="F295" s="12" t="inlineStr">
         <is>
-          <t>auditor</t>
+          <t>Audrey Lim</t>
         </is>
       </c>
       <c r="G295" s="12" t="inlineStr">
@@ -34619,7 +34619,7 @@
       </c>
       <c r="F296" s="12" t="inlineStr">
         <is>
-          <t>auditor</t>
+          <t>Audrey Lim</t>
         </is>
       </c>
       <c r="G296" s="12" t="inlineStr">
@@ -34700,7 +34700,7 @@
       </c>
       <c r="F297" s="12" t="inlineStr">
         <is>
-          <t>auditor</t>
+          <t>Audrey Lim</t>
         </is>
       </c>
       <c r="G297" s="12" t="inlineStr">
@@ -34781,7 +34781,7 @@
       </c>
       <c r="F298" s="12" t="inlineStr">
         <is>
-          <t>auditor</t>
+          <t>Audrey Lim</t>
         </is>
       </c>
       <c r="G298" s="12" t="inlineStr">
@@ -34943,7 +34943,7 @@
       </c>
       <c r="F300" s="12" t="inlineStr">
         <is>
-          <t>auditor</t>
+          <t>Audrey Lim</t>
         </is>
       </c>
       <c r="G300" s="12" t="inlineStr">
@@ -35024,7 +35024,7 @@
       </c>
       <c r="F301" s="12" t="inlineStr">
         <is>
-          <t>auditor</t>
+          <t>Audrey Lim</t>
         </is>
       </c>
       <c r="G301" s="12" t="inlineStr">
@@ -35105,7 +35105,7 @@
       </c>
       <c r="F302" s="12" t="inlineStr">
         <is>
-          <t>requestor</t>
+          <t>Rhea Santiago</t>
         </is>
       </c>
       <c r="G302" s="12" t="inlineStr">
@@ -35120,7 +35120,7 @@
       </c>
       <c r="I302" s="12" t="inlineStr">
         <is>
-          <t>1. After TC-UA-033.1-01, as requestor open the bell.</t>
+          <t>1. After TC-UA-033.1-01, as Rhea Santiago (Requestor) open the bell.</t>
         </is>
       </c>
       <c r="J302" s="12" t="inlineStr">
@@ -35267,7 +35267,7 @@
       </c>
       <c r="F304" s="12" t="inlineStr">
         <is>
-          <t>uamapprover</t>
+          <t>Ulysses Abad</t>
         </is>
       </c>
       <c r="G304" s="12" t="inlineStr">
@@ -35282,7 +35282,7 @@
       </c>
       <c r="I304" s="12" t="inlineStr">
         <is>
-          <t>1. As uamapprover2 open the bell after a submission to uamapprover.</t>
+          <t>1. As a second Approver open the bell after a submission to Ulysses Abad (Approver).</t>
         </is>
       </c>
       <c r="J304" s="12" t="inlineStr">
@@ -35348,7 +35348,7 @@
       </c>
       <c r="F305" s="12" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>Samuel Cruz</t>
         </is>
       </c>
       <c r="G305" s="12" t="inlineStr">
@@ -35429,7 +35429,7 @@
       </c>
       <c r="F306" s="12" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>Samuel Cruz</t>
         </is>
       </c>
       <c r="G306" s="12" t="inlineStr">
@@ -35510,7 +35510,7 @@
       </c>
       <c r="F307" s="12" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>Samuel Cruz</t>
         </is>
       </c>
       <c r="G307" s="12" t="inlineStr">
@@ -37320,7 +37320,7 @@
       </c>
       <c r="B40" s="12" t="inlineStr">
         <is>
-          <t>Please confirm the user ID format. The BRD asks for 'at least ten (10) alphanumeric characters' and 'supports a999999999 format' (p.13). the system checks new user IDs against a letter followed by nine digits (for example a013000196). Is the user ID the employee number, and how does it relate to the Windows ID? Embedded service accounts follow p_appname_description (p.12-13)..</t>
+          <t>Please confirm the user ID format. The BRD asks for 'at least ten (10) alphanumeric characters' and 'supports a999999999 format' (p.13). the system checks new user IDs against a letter followed by nine digits (for example a999999999). Is the user ID the employee number, and how does it relate to the Windows ID? Embedded service accounts follow p_appname_description (p.12-13)..</t>
         </is>
       </c>
       <c r="C40" s="12" t="inlineStr">
@@ -37655,7 +37655,7 @@
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>The UAT environment is ready with the users of the walkthrough users workbook and the SIT/UAT data.</t>
+          <t>The UAT environment is ready with the users of the walkthrough users workbook and the test data prepared for the walkthrough.</t>
         </is>
       </c>
     </row>
@@ -37685,7 +37685,7 @@
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>The testers are named (TD-11) and have their sign-in IDs; the passwords are issued separately by the iorta TechNXT Project Team.</t>
+          <t>The testers are named (TD-11) and receive their user IDs and passwords separately from the iorta TechNXT Project Team.</t>
         </is>
       </c>
     </row>
